--- a/source/dashboard_data.xlsx
+++ b/source/dashboard_data.xlsx
@@ -3325,7 +3325,7 @@
             <v>6050705-MBH 2F009</v>
           </cell>
           <cell r="E20">
-            <v>80</v>
+            <v>20</v>
           </cell>
           <cell r="F20">
             <v>1</v>
@@ -3361,13 +3361,13 @@
             <v>6220701-MVS MBH-VIP VIVO STORE-DD284</v>
           </cell>
           <cell r="E21">
-            <v>20</v>
+            <v>80</v>
           </cell>
           <cell r="F21">
             <v>3</v>
           </cell>
           <cell r="G21">
-            <v>6.66666666666667</v>
+            <v>26.6666666666667</v>
           </cell>
         </row>
         <row r="21">
@@ -5842,6 +5842,9 @@
   <sheetPr/>
   <dimension ref="A1:BQ48"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="4" max="4" width="50.8571428571429" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" s="1" t="s">
@@ -10415,7 +10418,7 @@
       </c>
       <c r="G20" s="102">
         <f>IFERROR(VLOOKUP(C20,'[1]TARGET THIS MONTH'!C:E,3,0),0)</f>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H20" s="103">
         <f>IFERROR(VLOOKUP(C20,'[1]TARGET THIS MONTH'!C:M,11,0),0)</f>
@@ -10427,11 +10430,11 @@
       </c>
       <c r="J20" s="104">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="K20" s="105">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-68</v>
       </c>
       <c r="L20" s="106">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",[1]PF!$A$5,"ID Store",$C20),0)</f>
@@ -10475,11 +10478,11 @@
       </c>
       <c r="V20" s="112">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="W20" s="113">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>-20</v>
       </c>
       <c r="X20" s="113">
         <f t="shared" si="10"/>
@@ -10487,7 +10490,7 @@
       </c>
       <c r="Y20" s="113">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="Z20" s="114">
         <f t="shared" si="12"/>
@@ -10503,7 +10506,7 @@
       </c>
       <c r="AC20" s="116">
         <f t="shared" si="15"/>
-        <v>0.333333333333333</v>
+        <v>2.83333333333333</v>
       </c>
       <c r="AD20" s="117">
         <f t="shared" si="16"/>
@@ -10687,7 +10690,7 @@
       </c>
       <c r="G21" s="102">
         <f>IFERROR(VLOOKUP(C21,'[1]TARGET THIS MONTH'!C:E,3,0),0)</f>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H21" s="103">
         <f>IFERROR(VLOOKUP(C21,'[1]TARGET THIS MONTH'!C:M,11,0),0)</f>
@@ -10699,11 +10702,11 @@
       </c>
       <c r="J21" s="104">
         <f t="shared" si="0"/>
-        <v>0.1125</v>
+        <v>0.45</v>
       </c>
       <c r="K21" s="105">
         <f t="shared" si="1"/>
-        <v>-71</v>
+        <v>-11</v>
       </c>
       <c r="L21" s="106">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",[1]PF!$A$5,"ID Store",$C21),0)</f>
@@ -10747,11 +10750,11 @@
       </c>
       <c r="V21" s="112">
         <f t="shared" si="8"/>
-        <v>0.5625</v>
+        <v>2.25</v>
       </c>
       <c r="W21" s="113">
         <f t="shared" si="9"/>
-        <v>-35</v>
+        <v>25</v>
       </c>
       <c r="X21" s="113">
         <f t="shared" si="10"/>
@@ -10759,7 +10762,7 @@
       </c>
       <c r="Y21" s="113">
         <f t="shared" si="11"/>
-        <v>-55</v>
+        <v>5</v>
       </c>
       <c r="Z21" s="114">
         <f t="shared" si="12"/>
@@ -10775,7 +10778,7 @@
       </c>
       <c r="AC21" s="116">
         <f t="shared" si="15"/>
-        <v>2.95833333333333</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="AD21" s="117">
         <f t="shared" si="16"/>

--- a/source/dashboard_data.xlsx
+++ b/source/dashboard_data.xlsx
@@ -1871,23 +1871,23 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="7" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1896,10 +1896,10 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1914,7 +1914,7 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1932,7 +1932,7 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1941,16 +1941,16 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1959,23 +1959,23 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1984,10 +1984,10 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2002,7 +2002,7 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2020,7 +2020,7 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2029,16 +2029,16 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2047,29 +2047,29 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2078,10 +2078,10 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2096,7 +2096,7 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2114,7 +2114,7 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2123,16 +2123,16 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -18022,19 +18022,19 @@
       <c r="D48" s="159"/>
       <c r="E48" s="159"/>
       <c r="F48" s="160">
-        <f>SUM(F5:F47)</f>
+        <f t="shared" ref="F48:I48" si="39">SUM(F5:F47)</f>
         <v>114</v>
       </c>
       <c r="G48" s="161">
-        <f>SUM(G5:G47)</f>
+        <f t="shared" si="39"/>
         <v>3400</v>
       </c>
       <c r="H48" s="162">
-        <f>SUM(H5:H47)</f>
+        <f t="shared" si="39"/>
         <v>15659000000</v>
       </c>
       <c r="I48" s="161">
-        <f>SUM(I5:I47)</f>
+        <f t="shared" si="39"/>
         <v>749</v>
       </c>
       <c r="J48" s="163">
@@ -18046,11 +18046,11 @@
         <v>-2651</v>
       </c>
       <c r="L48" s="159">
-        <f>SUM(L5:L47)</f>
+        <f t="shared" ref="L48:O48" si="40">SUM(L5:L47)</f>
         <v>146</v>
       </c>
       <c r="M48" s="159">
-        <f>SUM(M5:M47)</f>
+        <f t="shared" si="40"/>
         <v>273</v>
       </c>
       <c r="N48" s="165">
@@ -18058,7 +18058,7 @@
         <v>0.364485981308411</v>
       </c>
       <c r="O48" s="164">
-        <f>SUM(O5:O47)</f>
+        <f t="shared" si="40"/>
         <v>28</v>
       </c>
       <c r="P48" s="165">
@@ -18082,7 +18082,7 @@
         <v>-12736849000</v>
       </c>
       <c r="U48" s="168">
-        <f>SUM(U5:U47)</f>
+        <f t="shared" ref="U48:Z48" si="41">SUM(U5:U47)</f>
         <v>3745</v>
       </c>
       <c r="V48" s="163">
@@ -18094,7 +18094,7 @@
         <v>345</v>
       </c>
       <c r="X48" s="164">
-        <f>SUM(X5:X47)</f>
+        <f t="shared" si="41"/>
         <v>1365</v>
       </c>
       <c r="Y48" s="164">
@@ -18102,7 +18102,7 @@
         <v>-2035</v>
       </c>
       <c r="Z48" s="166">
-        <f>SUM(Z5:Z47)</f>
+        <f t="shared" si="41"/>
         <v>14610755000</v>
       </c>
       <c r="AA48" s="166">
@@ -18114,19 +18114,19 @@
         <v>0.933057985822849</v>
       </c>
       <c r="AC48" s="170">
-        <f>SUM(AC5:AC47)</f>
+        <f t="shared" ref="AC48:AF48" si="42">SUM(AC5:AC47)</f>
         <v>110.458333333333</v>
       </c>
       <c r="AD48" s="162">
-        <f>SUM(AD5:AD47)</f>
+        <f t="shared" si="42"/>
         <v>530702041.666667</v>
       </c>
       <c r="AE48" s="161">
-        <f>SUM(AE5:AE47)</f>
+        <f t="shared" si="42"/>
         <v>481</v>
       </c>
       <c r="AF48" s="171">
-        <f>SUM(AF5:AF47)</f>
+        <f t="shared" si="42"/>
         <v>28</v>
       </c>
       <c r="AG48" s="164">
@@ -18138,11 +18138,11 @@
         <v>-0.941787941787942</v>
       </c>
       <c r="AI48" s="172">
-        <f>SUM(AI5:AI47)</f>
+        <f t="shared" ref="AI48:AN48" si="43">SUM(AI5:AI47)</f>
         <v>3166</v>
       </c>
       <c r="AJ48" s="171">
-        <f>SUM(AJ5:AJ47)</f>
+        <f t="shared" si="43"/>
         <v>749</v>
       </c>
       <c r="AK48" s="164">
@@ -18154,11 +18154,11 @@
         <v>-0.763423878711308</v>
       </c>
       <c r="AM48" s="159">
-        <f>SUM(AM5:AM47)</f>
+        <f t="shared" si="43"/>
         <v>3166</v>
       </c>
       <c r="AN48" s="164">
-        <f>SUM(AN5:AN47)</f>
+        <f t="shared" si="43"/>
         <v>3745</v>
       </c>
       <c r="AO48" s="164">
@@ -18170,11 +18170,11 @@
         <v>0.182880606443462</v>
       </c>
       <c r="AQ48" s="159">
-        <f>SUM(AQ5:AQ47)</f>
+        <f t="shared" ref="AQ48:AV48" si="44">SUM(AQ5:AQ47)</f>
         <v>1431</v>
       </c>
       <c r="AR48" s="164">
-        <f>SUM(AR5:AR47)</f>
+        <f t="shared" si="44"/>
         <v>273</v>
       </c>
       <c r="AS48" s="164">
@@ -18186,11 +18186,11 @@
         <v>-0.809224318658281</v>
       </c>
       <c r="AU48" s="166">
-        <f>SUM(AU5:AU47)</f>
+        <f t="shared" si="44"/>
         <v>14942734000</v>
       </c>
       <c r="AV48" s="166">
-        <f>SUM(AV5:AV47)</f>
+        <f t="shared" si="44"/>
         <v>2922151000</v>
       </c>
       <c r="AW48" s="166">
@@ -18218,11 +18218,11 @@
         <v>-0.173388046342369</v>
       </c>
       <c r="BC48" s="161">
-        <f>SUM(BC5:BC47)</f>
+        <f t="shared" ref="BC48:BG48" si="45">SUM(BC5:BC47)</f>
         <v>340</v>
       </c>
       <c r="BD48" s="173">
-        <f>SUM(BD5:BD47)</f>
+        <f t="shared" si="45"/>
         <v>130</v>
       </c>
       <c r="BE48" s="165">
@@ -18230,11 +18230,11 @@
         <v>0.382352941176471</v>
       </c>
       <c r="BF48" s="166">
-        <f>SUM(BF5:BF47)</f>
+        <f t="shared" si="45"/>
         <v>76290000</v>
       </c>
       <c r="BG48" s="166">
-        <f>SUM(BG5:BG47)</f>
+        <f t="shared" si="45"/>
         <v>15004000</v>
       </c>
       <c r="BH48" s="165">
@@ -18242,11 +18242,11 @@
         <v>0.196670599030017</v>
       </c>
       <c r="BI48" s="166">
-        <f>SUM(BI5:BI47)</f>
+        <f t="shared" ref="BI48:BM48" si="46">SUM(BI5:BI47)</f>
         <v>15508000</v>
       </c>
       <c r="BJ48" s="166">
-        <f>SUM(BJ5:BJ47)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="BK48" s="165">
@@ -18254,11 +18254,11 @@
         <v>0</v>
       </c>
       <c r="BL48" s="164">
-        <f>SUM(BL5:BL47)</f>
+        <f t="shared" si="46"/>
         <v>102</v>
       </c>
       <c r="BM48" s="159">
-        <f>SUM(BM5:BM47)</f>
+        <f t="shared" si="46"/>
         <v>9</v>
       </c>
       <c r="BN48" s="165">
@@ -18313,13 +18313,13 @@
     <mergeCell ref="BO3:BO4"/>
     <mergeCell ref="BP3:BP4"/>
     <mergeCell ref="BQ3:BQ4"/>
-    <mergeCell ref="AI1:BB2"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="G1:H3"/>
     <mergeCell ref="AC1:AD3"/>
     <mergeCell ref="I1:T3"/>
     <mergeCell ref="U1:AB3"/>
     <mergeCell ref="AE1:AH3"/>
+    <mergeCell ref="AI1:BB2"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:C6">
     <cfRule type="duplicateValues" dxfId="0" priority="51"/>
@@ -18492,13 +18492,13 @@
       <formula>$F$2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5 C5:D5 A7 A9 A11 A13 A15 A17 A19 A21:A23 A25 A27 A29 A31 A33 A35 A37 A39:A41 A43 A45 A47">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A5:BQ47">
     <cfRule type="expression" dxfId="4" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5 C5:D5 A7 A9 A11 A13 A15 A17 A19 A21:A23 A25 A27 A29 A31 A33 A35 A37 A39:A41 A43 A45 A47">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6 A8 A10 A12 A14 A16 A18 A20 A24 A26 A28 A30 A32 A34 A36 A38 A42 A44 A46">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>

--- a/source/dashboard_data.xlsx
+++ b/source/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michael/Desktop/05 Store Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BA898F-D1C0-C64D-83AC-D6323B3C1F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF68AD2F-E436-AB49-ABA7-07DEEC201F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="32740" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="32740" windowHeight="15440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5735,14 +5735,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
         <row r="5">
           <cell r="A5">
@@ -6476,13 +6476,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
       <sheetData sheetId="17">
         <row r="5">
           <cell r="A5" t="str">
@@ -6505,7 +6505,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="21" refreshError="1"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23">
         <row r="6">
@@ -6514,7 +6514,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="24" refreshError="1"/>
       <sheetData sheetId="25">
         <row r="10">
           <cell r="B10">
@@ -8712,11 +8712,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="26"/>
+      <sheetData sheetId="26" refreshError="1"/>
       <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
       <sheetData sheetId="31">
         <row r="2">
           <cell r="E2" t="str">
@@ -10897,9 +10897,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
       <sheetData sheetId="35"/>
       <sheetData sheetId="36">
         <row r="6">
@@ -12013,14 +12013,14 @@
       <c r="B2" s="173"/>
       <c r="C2" s="173"/>
       <c r="D2" s="21">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="21">
         <v>11</v>
       </c>
       <c r="F2" s="22">
         <f>E2/D2</f>
-        <v>0.36666666666666664</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="G2" s="176"/>
       <c r="H2" s="177"/>
@@ -12463,43 +12463,43 @@
       </c>
       <c r="U5" s="57">
         <f t="shared" ref="U5:U47" si="7">I5/$E$2*$D$2</f>
-        <v>79.090909090909093</v>
+        <v>81.72727272727272</v>
       </c>
       <c r="V5" s="58">
         <f t="shared" ref="V5:V47" si="8">IFERROR(U5/G5,0)</f>
-        <v>0.65909090909090906</v>
+        <v>0.68106060606060603</v>
       </c>
       <c r="W5" s="59">
         <f t="shared" ref="W5:W48" si="9">U5-G5</f>
-        <v>-40.909090909090907</v>
+        <v>-38.27272727272728</v>
       </c>
       <c r="X5" s="59">
         <f t="shared" ref="X5:X47" si="10">M5/$E$2*$D$2</f>
-        <v>38.18181818181818</v>
+        <v>39.454545454545453</v>
       </c>
       <c r="Y5" s="59">
         <f t="shared" ref="Y5:Y48" si="11">X5-G5</f>
-        <v>-81.818181818181813</v>
+        <v>-80.545454545454547</v>
       </c>
       <c r="Z5" s="60">
         <f t="shared" ref="Z5:Z47" si="12">R5/$E$2*$D$2</f>
-        <v>328011818.18181819</v>
+        <v>338945545.4545455</v>
       </c>
       <c r="AA5" s="60">
         <f t="shared" ref="AA5:AA48" si="13">Z5-H5</f>
-        <v>-511988181.81818181</v>
+        <v>-501054454.5454545</v>
       </c>
       <c r="AB5" s="61">
         <f t="shared" ref="AB5:AB47" si="14">IFERROR(Z5/H5,0)</f>
-        <v>0.39049025974025975</v>
+        <v>0.4035066017316018</v>
       </c>
       <c r="AC5" s="62">
         <f t="shared" ref="AC5:AC47" si="15">IFERROR(($G5-$I5)/($D$2-$E$2),0)</f>
-        <v>4.7894736842105265</v>
+        <v>4.55</v>
       </c>
       <c r="AD5" s="63">
         <f t="shared" ref="AD5:AD47" si="16">IFERROR(($H5-$R5)/($D$2-$E$2),0)</f>
-        <v>37880473.684210524</v>
+        <v>35986450</v>
       </c>
       <c r="AE5" s="48">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C5),0)</f>
@@ -12539,15 +12539,15 @@
       </c>
       <c r="AN5" s="51">
         <f t="shared" ref="AN5:AN47" si="22">VLOOKUP(C:C,C:U,19,0)</f>
-        <v>79.090909090909093</v>
+        <v>81.72727272727272</v>
       </c>
       <c r="AO5" s="51">
         <f t="shared" ref="AO5:AO48" si="23">AN5-AM5</f>
-        <v>-30.909090909090907</v>
+        <v>-28.27272727272728</v>
       </c>
       <c r="AP5" s="53">
         <f t="shared" ref="AP5:AP47" si="24">IFERROR(AO5/AM5,0)</f>
-        <v>-0.28099173553719003</v>
+        <v>-0.25702479338842982</v>
       </c>
       <c r="AQ5" s="52">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C5,"Segment Price","3mio&gt;"),0)</f>
@@ -12587,15 +12587,15 @@
       </c>
       <c r="AZ5" s="55">
         <f t="shared" ref="AZ5:AZ47" si="31">IFERROR(Z5/U5,0)</f>
-        <v>4147275.8620689656</v>
+        <v>4147275.8620689665</v>
       </c>
       <c r="BA5" s="55">
         <f t="shared" ref="BA5:BA48" si="32">AZ5-AY5</f>
-        <v>-2111247.9474548441</v>
+        <v>-2111247.9474548432</v>
       </c>
       <c r="BB5" s="65">
         <f t="shared" ref="BB5:BB47" si="33">IFERROR(BA5/AY5,0)</f>
-        <v>-0.33733960462722629</v>
+        <v>-0.33733960462722618</v>
       </c>
       <c r="BC5" s="48">
         <f>IFERROR(VLOOKUP(C5,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -12735,43 +12735,43 @@
       </c>
       <c r="U6" s="87">
         <f t="shared" si="7"/>
-        <v>286.36363636363637</v>
+        <v>295.90909090909088</v>
       </c>
       <c r="V6" s="88">
         <f t="shared" si="8"/>
-        <v>1.1013986013986015</v>
+        <v>1.1381118881118879</v>
       </c>
       <c r="W6" s="89">
         <f t="shared" si="9"/>
-        <v>26.363636363636374</v>
+        <v>35.909090909090878</v>
       </c>
       <c r="X6" s="89">
         <f t="shared" si="10"/>
-        <v>114.54545454545455</v>
+        <v>118.36363636363637</v>
       </c>
       <c r="Y6" s="89">
         <f t="shared" si="11"/>
-        <v>-145.45454545454544</v>
+        <v>-141.63636363636363</v>
       </c>
       <c r="Z6" s="90">
         <f t="shared" si="12"/>
-        <v>1042622727.2727273</v>
+        <v>1077376818.181818</v>
       </c>
       <c r="AA6" s="90">
         <f t="shared" si="13"/>
-        <v>80622727.272727251</v>
+        <v>115376818.18181801</v>
       </c>
       <c r="AB6" s="91">
         <f t="shared" si="14"/>
-        <v>1.0838074088074088</v>
+        <v>1.1199343224343223</v>
       </c>
       <c r="AC6" s="92">
         <f t="shared" si="15"/>
-        <v>8.1578947368421044</v>
+        <v>7.75</v>
       </c>
       <c r="AD6" s="93">
         <f t="shared" si="16"/>
-        <v>30510789.47368421</v>
+        <v>28985250</v>
       </c>
       <c r="AE6" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C6),0)</f>
@@ -12811,15 +12811,15 @@
       </c>
       <c r="AN6" s="81">
         <f t="shared" si="22"/>
-        <v>286.36363636363637</v>
+        <v>295.90909090909088</v>
       </c>
       <c r="AO6" s="81">
         <f t="shared" si="23"/>
-        <v>16.363636363636374</v>
+        <v>25.909090909090878</v>
       </c>
       <c r="AP6" s="83">
         <f t="shared" si="24"/>
-        <v>6.0606060606060642E-2</v>
+        <v>9.5959595959595842E-2</v>
       </c>
       <c r="AQ6" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C6,"Segment Price","3mio&gt;"),0)</f>
@@ -13007,43 +13007,43 @@
       </c>
       <c r="U7" s="87">
         <f t="shared" si="7"/>
-        <v>294.54545454545456</v>
+        <v>304.36363636363637</v>
       </c>
       <c r="V7" s="88">
         <f t="shared" si="8"/>
-        <v>1.1328671328671329</v>
+        <v>1.1706293706293707</v>
       </c>
       <c r="W7" s="89">
         <f t="shared" si="9"/>
-        <v>34.545454545454561</v>
+        <v>44.363636363636374</v>
       </c>
       <c r="X7" s="89">
         <f t="shared" si="10"/>
-        <v>79.090909090909093</v>
+        <v>81.72727272727272</v>
       </c>
       <c r="Y7" s="89">
         <f t="shared" si="11"/>
-        <v>-180.90909090909091</v>
+        <v>-178.27272727272728</v>
       </c>
       <c r="Z7" s="90">
         <f t="shared" si="12"/>
-        <v>927796363.63636363</v>
+        <v>958722909.090909</v>
       </c>
       <c r="AA7" s="90">
         <f t="shared" si="13"/>
-        <v>-34203636.363636374</v>
+        <v>-3277090.9090909958</v>
       </c>
       <c r="AB7" s="91">
         <f t="shared" si="14"/>
-        <v>0.96444528444528443</v>
+        <v>0.99659346059346055</v>
       </c>
       <c r="AC7" s="92">
         <f t="shared" si="15"/>
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" s="93">
         <f t="shared" si="16"/>
-        <v>32726736.842105262</v>
+        <v>31090400</v>
       </c>
       <c r="AE7" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C7),0)</f>
@@ -13083,15 +13083,15 @@
       </c>
       <c r="AN7" s="81">
         <f t="shared" si="22"/>
-        <v>294.54545454545456</v>
+        <v>304.36363636363637</v>
       </c>
       <c r="AO7" s="81">
         <f t="shared" si="23"/>
-        <v>24.545454545454561</v>
+        <v>34.363636363636374</v>
       </c>
       <c r="AP7" s="83">
         <f t="shared" si="24"/>
-        <v>9.0909090909090967E-2</v>
+        <v>0.12727272727272732</v>
       </c>
       <c r="AQ7" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C7,"Segment Price","3mio&gt;"),0)</f>
@@ -13131,15 +13131,15 @@
       </c>
       <c r="AZ7" s="85">
         <f t="shared" si="31"/>
-        <v>3149925.9259259258</v>
+        <v>3149925.9259259254</v>
       </c>
       <c r="BA7" s="85">
         <f t="shared" si="32"/>
-        <v>-164074.07407407416</v>
+        <v>-164074.07407407463</v>
       </c>
       <c r="BB7" s="95">
         <f t="shared" si="33"/>
-        <v>-4.950937660654018E-2</v>
+        <v>-4.9509376606540319E-2</v>
       </c>
       <c r="BC7" s="78">
         <f>IFERROR(VLOOKUP(C7,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -13279,43 +13279,43 @@
       </c>
       <c r="U8" s="87">
         <f t="shared" si="7"/>
-        <v>158.18181818181819</v>
+        <v>163.45454545454544</v>
       </c>
       <c r="V8" s="88">
         <f t="shared" si="8"/>
-        <v>1.3181818181818181</v>
+        <v>1.3621212121212121</v>
       </c>
       <c r="W8" s="89">
         <f t="shared" si="9"/>
-        <v>38.181818181818187</v>
+        <v>43.454545454545439</v>
       </c>
       <c r="X8" s="89">
         <f t="shared" si="10"/>
-        <v>27.272727272727273</v>
+        <v>28.18181818181818</v>
       </c>
       <c r="Y8" s="89">
         <f t="shared" si="11"/>
-        <v>-92.72727272727272</v>
+        <v>-91.818181818181813</v>
       </c>
       <c r="Z8" s="90">
         <f t="shared" si="12"/>
-        <v>412478181.81818181</v>
+        <v>426227454.5454545</v>
       </c>
       <c r="AA8" s="90">
         <f t="shared" si="13"/>
-        <v>-7521818.1818181872</v>
+        <v>6227454.5454545021</v>
       </c>
       <c r="AB8" s="91">
         <f t="shared" si="14"/>
-        <v>0.98209090909090913</v>
+        <v>1.0148272727272727</v>
       </c>
       <c r="AC8" s="92">
         <f t="shared" si="15"/>
-        <v>3.263157894736842</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" s="93">
         <f t="shared" si="16"/>
-        <v>14145157.894736841</v>
+        <v>13437900</v>
       </c>
       <c r="AE8" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C8),0)</f>
@@ -13355,15 +13355,15 @@
       </c>
       <c r="AN8" s="81">
         <f t="shared" si="22"/>
-        <v>158.18181818181819</v>
+        <v>163.45454545454544</v>
       </c>
       <c r="AO8" s="81">
         <f t="shared" si="23"/>
-        <v>53.181818181818187</v>
+        <v>58.454545454545439</v>
       </c>
       <c r="AP8" s="83">
         <f t="shared" si="24"/>
-        <v>0.50649350649350655</v>
+        <v>0.5567099567099566</v>
       </c>
       <c r="AQ8" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C8,"Segment Price","3mio&gt;"),0)</f>
@@ -13551,43 +13551,43 @@
       </c>
       <c r="U9" s="87">
         <f t="shared" si="7"/>
-        <v>422.72727272727275</v>
+        <v>436.81818181818187</v>
       </c>
       <c r="V9" s="88">
         <f t="shared" si="8"/>
-        <v>1.3210227272727273</v>
+        <v>1.3650568181818183</v>
       </c>
       <c r="W9" s="89">
         <f t="shared" si="9"/>
-        <v>102.72727272727275</v>
+        <v>116.81818181818187</v>
       </c>
       <c r="X9" s="89">
         <f t="shared" si="10"/>
-        <v>92.72727272727272</v>
+        <v>95.818181818181813</v>
       </c>
       <c r="Y9" s="89">
         <f t="shared" si="11"/>
-        <v>-227.27272727272728</v>
+        <v>-224.18181818181819</v>
       </c>
       <c r="Z9" s="90">
         <f t="shared" si="12"/>
-        <v>1208031818.1818182</v>
+        <v>1248299545.4545455</v>
       </c>
       <c r="AA9" s="90">
         <f t="shared" si="13"/>
-        <v>88031818.181818247</v>
+        <v>128299545.4545455</v>
       </c>
       <c r="AB9" s="91">
         <f t="shared" si="14"/>
-        <v>1.0785998376623378</v>
+        <v>1.1145531655844156</v>
       </c>
       <c r="AC9" s="92">
         <f t="shared" si="15"/>
-        <v>8.6842105263157894</v>
+        <v>8.25</v>
       </c>
       <c r="AD9" s="93">
         <f t="shared" si="16"/>
-        <v>35634473.684210524</v>
+        <v>33852750</v>
       </c>
       <c r="AE9" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C9),0)</f>
@@ -13627,15 +13627,15 @@
       </c>
       <c r="AN9" s="81">
         <f t="shared" si="22"/>
-        <v>422.72727272727275</v>
+        <v>436.81818181818187</v>
       </c>
       <c r="AO9" s="81">
         <f t="shared" si="23"/>
-        <v>69.727272727272748</v>
+        <v>83.81818181818187</v>
       </c>
       <c r="AP9" s="83">
         <f t="shared" si="24"/>
-        <v>0.19752768477980948</v>
+        <v>0.23744527427246989</v>
       </c>
       <c r="AQ9" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C9,"Segment Price","3mio&gt;"),0)</f>
@@ -13823,43 +13823,43 @@
       </c>
       <c r="U10" s="87">
         <f t="shared" si="7"/>
-        <v>158.18181818181819</v>
+        <v>163.45454545454544</v>
       </c>
       <c r="V10" s="88">
         <f t="shared" si="8"/>
-        <v>1.4380165289256199</v>
+        <v>1.4859504132231403</v>
       </c>
       <c r="W10" s="89">
         <f t="shared" si="9"/>
-        <v>48.181818181818187</v>
+        <v>53.454545454545439</v>
       </c>
       <c r="X10" s="89">
         <f t="shared" si="10"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="Y10" s="89">
         <f t="shared" si="11"/>
-        <v>-77.27272727272728</v>
+        <v>-76.181818181818187</v>
       </c>
       <c r="Z10" s="90">
         <f t="shared" si="12"/>
-        <v>428296363.63636363</v>
+        <v>442572909.09090912</v>
       </c>
       <c r="AA10" s="90">
         <f t="shared" si="13"/>
-        <v>43296363.636363626</v>
+        <v>57572909.090909123</v>
       </c>
       <c r="AB10" s="91">
         <f t="shared" si="14"/>
-        <v>1.1124580873671783</v>
+        <v>1.1495400236127509</v>
       </c>
       <c r="AC10" s="92">
         <f t="shared" si="15"/>
-        <v>2.736842105263158</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" s="93">
         <f t="shared" si="16"/>
-        <v>11997789.47368421</v>
+        <v>11397900</v>
       </c>
       <c r="AE10" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C10),0)</f>
@@ -13899,15 +13899,15 @@
       </c>
       <c r="AN10" s="81">
         <f t="shared" si="22"/>
-        <v>158.18181818181819</v>
+        <v>163.45454545454544</v>
       </c>
       <c r="AO10" s="81">
         <f t="shared" si="23"/>
-        <v>38.181818181818187</v>
+        <v>43.454545454545439</v>
       </c>
       <c r="AP10" s="83">
         <f t="shared" si="24"/>
-        <v>0.31818181818181823</v>
+        <v>0.36212121212121201</v>
       </c>
       <c r="AQ10" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C10,"Segment Price","3mio&gt;"),0)</f>
@@ -13947,15 +13947,15 @@
       </c>
       <c r="AZ10" s="85">
         <f t="shared" si="31"/>
-        <v>2707620.6896551722</v>
+        <v>2707620.6896551726</v>
       </c>
       <c r="BA10" s="85">
         <f t="shared" si="32"/>
-        <v>-653879.31034482783</v>
+        <v>-653879.31034482736</v>
       </c>
       <c r="BB10" s="95">
         <f t="shared" si="33"/>
-        <v>-0.19452009827304115</v>
+        <v>-0.19452009827304101</v>
       </c>
       <c r="BC10" s="78">
         <f>IFERROR(VLOOKUP(C10,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -14095,43 +14095,43 @@
       </c>
       <c r="U11" s="87">
         <f t="shared" si="7"/>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="V11" s="88">
         <f t="shared" si="8"/>
-        <v>0.75</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="W11" s="89">
         <f t="shared" si="9"/>
-        <v>-30</v>
+        <v>-27</v>
       </c>
       <c r="X11" s="89">
         <f t="shared" si="10"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="Y11" s="89">
         <f t="shared" si="11"/>
-        <v>-76.36363636363636</v>
+        <v>-74.909090909090907</v>
       </c>
       <c r="Z11" s="90">
         <f t="shared" si="12"/>
-        <v>565273636.36363637</v>
+        <v>584116090.909091</v>
       </c>
       <c r="AA11" s="90">
         <f t="shared" si="13"/>
-        <v>-274726363.63636363</v>
+        <v>-255883909.090909</v>
       </c>
       <c r="AB11" s="91">
         <f t="shared" si="14"/>
-        <v>0.67294480519480526</v>
+        <v>0.6953762987012988</v>
       </c>
       <c r="AC11" s="92">
         <f t="shared" si="15"/>
-        <v>4.5789473684210522</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="AD11" s="93">
         <f t="shared" si="16"/>
-        <v>33301736.842105262</v>
+        <v>31636650</v>
       </c>
       <c r="AE11" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C11),0)</f>
@@ -14171,15 +14171,15 @@
       </c>
       <c r="AN11" s="81">
         <f t="shared" si="22"/>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AO11" s="81">
         <f t="shared" si="23"/>
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="AP11" s="83">
         <f t="shared" si="24"/>
-        <v>-0.1891891891891892</v>
+        <v>-0.16216216216216217</v>
       </c>
       <c r="AQ11" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C11,"Segment Price","3mio&gt;"),0)</f>
@@ -14219,15 +14219,15 @@
       </c>
       <c r="AZ11" s="85">
         <f t="shared" si="31"/>
-        <v>6280818.1818181816</v>
+        <v>6280818.1818181826</v>
       </c>
       <c r="BA11" s="85">
         <f t="shared" si="32"/>
-        <v>1299675.3246753244</v>
+        <v>1299675.3246753253</v>
       </c>
       <c r="BB11" s="95">
         <f t="shared" si="33"/>
-        <v>0.26091910269379576</v>
+        <v>0.26091910269379592</v>
       </c>
       <c r="BC11" s="78">
         <f>IFERROR(VLOOKUP(C11,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -14367,43 +14367,43 @@
       </c>
       <c r="U12" s="87">
         <f t="shared" si="7"/>
-        <v>57.272727272727273</v>
+        <v>59.181818181818187</v>
       </c>
       <c r="V12" s="88">
         <f t="shared" si="8"/>
-        <v>1.1454545454545455</v>
+        <v>1.1836363636363638</v>
       </c>
       <c r="W12" s="89">
         <f t="shared" si="9"/>
-        <v>7.2727272727272734</v>
+        <v>9.181818181818187</v>
       </c>
       <c r="X12" s="89">
         <f t="shared" si="10"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="Y12" s="89">
         <f t="shared" si="11"/>
-        <v>-17.272727272727273</v>
+        <v>-16.181818181818187</v>
       </c>
       <c r="Z12" s="90">
         <f t="shared" si="12"/>
-        <v>449942727.27272725</v>
+        <v>464940818.18181813</v>
       </c>
       <c r="AA12" s="90">
         <f t="shared" si="13"/>
-        <v>99942727.272727251</v>
+        <v>114940818.18181813</v>
       </c>
       <c r="AB12" s="91">
         <f t="shared" si="14"/>
-        <v>1.2855506493506492</v>
+        <v>1.3284023376623375</v>
       </c>
       <c r="AC12" s="92">
         <f t="shared" si="15"/>
-        <v>1.5263157894736843</v>
+        <v>1.45</v>
       </c>
       <c r="AD12" s="93">
         <f t="shared" si="16"/>
-        <v>9737947.3684210535</v>
+        <v>9251050</v>
       </c>
       <c r="AE12" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C12),0)</f>
@@ -14443,15 +14443,15 @@
       </c>
       <c r="AN12" s="81">
         <f t="shared" si="22"/>
-        <v>57.272727272727273</v>
+        <v>59.181818181818187</v>
       </c>
       <c r="AO12" s="81">
         <f t="shared" si="23"/>
-        <v>19.272727272727273</v>
+        <v>21.181818181818187</v>
       </c>
       <c r="AP12" s="83">
         <f t="shared" si="24"/>
-        <v>0.50717703349282295</v>
+        <v>0.55741626794258392</v>
       </c>
       <c r="AQ12" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C12,"Segment Price","3mio&gt;"),0)</f>
@@ -14491,15 +14491,15 @@
       </c>
       <c r="AZ12" s="85">
         <f t="shared" si="31"/>
-        <v>7856142.8571428563</v>
+        <v>7856142.8571428554</v>
       </c>
       <c r="BA12" s="85">
         <f t="shared" si="32"/>
-        <v>937142.85714285634</v>
+        <v>937142.85714285541</v>
       </c>
       <c r="BB12" s="95">
         <f t="shared" si="33"/>
-        <v>0.13544484132719414</v>
+        <v>0.13544484132719403</v>
       </c>
       <c r="BC12" s="78">
         <f>IFERROR(VLOOKUP(C12,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -14639,43 +14639,43 @@
       </c>
       <c r="U13" s="87">
         <f t="shared" si="7"/>
-        <v>106.36363636363636</v>
+        <v>109.90909090909091</v>
       </c>
       <c r="V13" s="88">
         <f t="shared" si="8"/>
-        <v>1.0636363636363635</v>
+        <v>1.0990909090909091</v>
       </c>
       <c r="W13" s="89">
         <f t="shared" si="9"/>
-        <v>6.3636363636363598</v>
+        <v>9.9090909090909065</v>
       </c>
       <c r="X13" s="89">
         <f t="shared" si="10"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="Y13" s="89">
         <f t="shared" si="11"/>
-        <v>-56.36363636363636</v>
+        <v>-54.909090909090907</v>
       </c>
       <c r="Z13" s="90">
         <f t="shared" si="12"/>
-        <v>366711818.18181819</v>
+        <v>378935545.4545455</v>
       </c>
       <c r="AA13" s="90">
         <f t="shared" si="13"/>
-        <v>-63288181.818181813</v>
+        <v>-51064454.545454502</v>
       </c>
       <c r="AB13" s="91">
         <f t="shared" si="14"/>
-        <v>0.85281818181818181</v>
+        <v>0.88124545454545467</v>
       </c>
       <c r="AC13" s="92">
         <f t="shared" si="15"/>
-        <v>3.2105263157894739</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" s="93">
         <f t="shared" si="16"/>
-        <v>15554684.210526315</v>
+        <v>14776950</v>
       </c>
       <c r="AE13" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C13),0)</f>
@@ -14715,15 +14715,15 @@
       </c>
       <c r="AN13" s="81">
         <f t="shared" si="22"/>
-        <v>106.36363636363636</v>
+        <v>109.90909090909091</v>
       </c>
       <c r="AO13" s="81">
         <f t="shared" si="23"/>
-        <v>-1.6363636363636402</v>
+        <v>1.9090909090909065</v>
       </c>
       <c r="AP13" s="83">
         <f t="shared" si="24"/>
-        <v>-1.5151515151515187E-2</v>
+        <v>1.7676767676767652E-2</v>
       </c>
       <c r="AQ13" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C13,"Segment Price","3mio&gt;"),0)</f>
@@ -14911,43 +14911,43 @@
       </c>
       <c r="U14" s="87">
         <f t="shared" si="7"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="V14" s="88">
         <f t="shared" si="8"/>
-        <v>0.81818181818181823</v>
+        <v>0.84545454545454557</v>
       </c>
       <c r="W14" s="89">
         <f t="shared" si="9"/>
-        <v>-10.909090909090907</v>
+        <v>-9.2727272727272663</v>
       </c>
       <c r="X14" s="89">
         <f t="shared" si="10"/>
-        <v>27.272727272727273</v>
+        <v>28.18181818181818</v>
       </c>
       <c r="Y14" s="89">
         <f t="shared" si="11"/>
-        <v>-32.727272727272727</v>
+        <v>-31.81818181818182</v>
       </c>
       <c r="Z14" s="90">
         <f t="shared" si="12"/>
-        <v>193860000</v>
+        <v>200322000</v>
       </c>
       <c r="AA14" s="90">
         <f t="shared" si="13"/>
-        <v>-64140000</v>
+        <v>-57678000</v>
       </c>
       <c r="AB14" s="91">
         <f t="shared" si="14"/>
-        <v>0.75139534883720926</v>
+        <v>0.77644186046511632</v>
       </c>
       <c r="AC14" s="92">
         <f t="shared" si="15"/>
-        <v>2.2105263157894739</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" s="93">
         <f t="shared" si="16"/>
-        <v>9837789.4736842103</v>
+        <v>9345900</v>
       </c>
       <c r="AE14" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C14),0)</f>
@@ -14987,15 +14987,15 @@
       </c>
       <c r="AN14" s="81">
         <f t="shared" si="22"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="AO14" s="81">
         <f t="shared" si="23"/>
-        <v>-4.9090909090909065</v>
+        <v>-3.2727272727272663</v>
       </c>
       <c r="AP14" s="83">
         <f t="shared" si="24"/>
-        <v>-9.0909090909090856E-2</v>
+        <v>-6.060606060606049E-2</v>
       </c>
       <c r="AQ14" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C14,"Segment Price","3mio&gt;"),0)</f>
@@ -15035,15 +15035,15 @@
       </c>
       <c r="AZ14" s="85">
         <f t="shared" si="31"/>
-        <v>3949000</v>
+        <v>3948999.9999999995</v>
       </c>
       <c r="BA14" s="85">
         <f t="shared" si="32"/>
-        <v>507692.30769230751</v>
+        <v>507692.30769230705</v>
       </c>
       <c r="BB14" s="95">
         <f t="shared" si="33"/>
-        <v>0.14752889107450204</v>
+        <v>0.1475288910745019</v>
       </c>
       <c r="BC14" s="78">
         <f>IFERROR(VLOOKUP(C14,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -15183,43 +15183,43 @@
       </c>
       <c r="U15" s="87">
         <f t="shared" si="7"/>
-        <v>70.909090909090907</v>
+        <v>73.27272727272728</v>
       </c>
       <c r="V15" s="88">
         <f t="shared" si="8"/>
-        <v>1.4181818181818182</v>
+        <v>1.4654545454545456</v>
       </c>
       <c r="W15" s="89">
         <f t="shared" si="9"/>
-        <v>20.909090909090907</v>
+        <v>23.27272727272728</v>
       </c>
       <c r="X15" s="89">
         <f t="shared" si="10"/>
-        <v>35.454545454545453</v>
+        <v>36.63636363636364</v>
       </c>
       <c r="Y15" s="89">
         <f t="shared" si="11"/>
-        <v>-14.545454545454547</v>
+        <v>-13.36363636363636</v>
       </c>
       <c r="Z15" s="90">
         <f t="shared" si="12"/>
-        <v>284110909.09090912</v>
+        <v>293581272.72727275</v>
       </c>
       <c r="AA15" s="90">
         <f t="shared" si="13"/>
-        <v>69110909.090909123</v>
+        <v>78581272.727272749</v>
       </c>
       <c r="AB15" s="91">
         <f t="shared" si="14"/>
-        <v>1.3214460887949262</v>
+        <v>1.365494291754757</v>
       </c>
       <c r="AC15" s="92">
         <f t="shared" si="15"/>
-        <v>1.263157894736842</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" s="93">
         <f t="shared" si="16"/>
-        <v>5832947.3684210526</v>
+        <v>5541300</v>
       </c>
       <c r="AE15" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C15),0)</f>
@@ -15259,15 +15259,15 @@
       </c>
       <c r="AN15" s="81">
         <f t="shared" si="22"/>
-        <v>70.909090909090907</v>
+        <v>73.27272727272728</v>
       </c>
       <c r="AO15" s="81">
         <f t="shared" si="23"/>
-        <v>14.909090909090907</v>
+        <v>17.27272727272728</v>
       </c>
       <c r="AP15" s="83">
         <f t="shared" si="24"/>
-        <v>0.26623376623376621</v>
+        <v>0.30844155844155857</v>
       </c>
       <c r="AQ15" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C15,"Segment Price","3mio&gt;"),0)</f>
@@ -15307,15 +15307,15 @@
       </c>
       <c r="AZ15" s="85">
         <f t="shared" si="31"/>
-        <v>4006692.3076923084</v>
+        <v>4006692.3076923075</v>
       </c>
       <c r="BA15" s="85">
         <f t="shared" si="32"/>
-        <v>-981196.58119658055</v>
+        <v>-981196.58119658148</v>
       </c>
       <c r="BB15" s="95">
         <f t="shared" si="33"/>
-        <v>-0.19671580563518801</v>
+        <v>-0.1967158056351882</v>
       </c>
       <c r="BC15" s="78">
         <f>IFERROR(VLOOKUP(C15,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -15455,43 +15455,43 @@
       </c>
       <c r="U16" s="87">
         <f t="shared" si="7"/>
-        <v>51.81818181818182</v>
+        <v>53.545454545454547</v>
       </c>
       <c r="V16" s="88">
         <f t="shared" si="8"/>
-        <v>0.86363636363636365</v>
+        <v>0.89242424242424245</v>
       </c>
       <c r="W16" s="89">
         <f t="shared" si="9"/>
-        <v>-8.1818181818181799</v>
+        <v>-6.4545454545454533</v>
       </c>
       <c r="X16" s="89">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y16" s="89">
         <f t="shared" si="11"/>
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="Z16" s="90">
         <f t="shared" si="12"/>
-        <v>258766363.63636366</v>
+        <v>267391909.09090909</v>
       </c>
       <c r="AA16" s="90">
         <f t="shared" si="13"/>
-        <v>766363.63636365533</v>
+        <v>9391909.0909090936</v>
       </c>
       <c r="AB16" s="91">
         <f t="shared" si="14"/>
-        <v>1.0029704016913319</v>
+        <v>1.0364027484143763</v>
       </c>
       <c r="AC16" s="92">
         <f t="shared" si="15"/>
-        <v>2.1578947368421053</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="AD16" s="93">
         <f t="shared" si="16"/>
-        <v>8585210.5263157897</v>
+        <v>8155950</v>
       </c>
       <c r="AE16" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C16),0)</f>
@@ -15531,15 +15531,15 @@
       </c>
       <c r="AN16" s="81">
         <f t="shared" si="22"/>
-        <v>51.81818181818182</v>
+        <v>53.545454545454547</v>
       </c>
       <c r="AO16" s="81">
         <f t="shared" si="23"/>
-        <v>-13.18181818181818</v>
+        <v>-11.454545454545453</v>
       </c>
       <c r="AP16" s="83">
         <f t="shared" si="24"/>
-        <v>-0.20279720279720276</v>
+        <v>-0.17622377622377619</v>
       </c>
       <c r="AQ16" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C16,"Segment Price","3mio&gt;"),0)</f>
@@ -15727,43 +15727,43 @@
       </c>
       <c r="U17" s="87">
         <f t="shared" si="7"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="V17" s="88">
         <f t="shared" si="8"/>
-        <v>1.0909090909090908</v>
+        <v>1.1272727272727272</v>
       </c>
       <c r="W17" s="89">
         <f t="shared" si="9"/>
-        <v>2.7272727272727266</v>
+        <v>3.818181818181813</v>
       </c>
       <c r="X17" s="89">
         <f t="shared" si="10"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Y17" s="89">
         <f t="shared" si="11"/>
-        <v>-10.90909090909091</v>
+        <v>-10.272727272727273</v>
       </c>
       <c r="Z17" s="90">
         <f t="shared" si="12"/>
-        <v>158694545.45454544</v>
+        <v>163984363.63636363</v>
       </c>
       <c r="AA17" s="90">
         <f t="shared" si="13"/>
-        <v>-51305454.545454562</v>
+        <v>-46015636.363636374</v>
       </c>
       <c r="AB17" s="91">
         <f t="shared" si="14"/>
-        <v>0.75568831168831163</v>
+        <v>0.78087792207792206</v>
       </c>
       <c r="AC17" s="92">
         <f t="shared" si="15"/>
-        <v>0.94736842105263153</v>
+        <v>0.9</v>
       </c>
       <c r="AD17" s="93">
         <f t="shared" si="16"/>
-        <v>7990105.2631578948</v>
+        <v>7590600</v>
       </c>
       <c r="AE17" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C17),0)</f>
@@ -15803,15 +15803,15 @@
       </c>
       <c r="AN17" s="81">
         <f t="shared" si="22"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="AO17" s="81">
         <f t="shared" si="23"/>
-        <v>4.7272727272727266</v>
+        <v>5.818181818181813</v>
       </c>
       <c r="AP17" s="83">
         <f t="shared" si="24"/>
-        <v>0.1688311688311688</v>
+        <v>0.20779220779220761</v>
       </c>
       <c r="AQ17" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C17,"Segment Price","3mio&gt;"),0)</f>
@@ -15999,43 +15999,43 @@
       </c>
       <c r="U18" s="87">
         <f t="shared" si="7"/>
-        <v>38.18181818181818</v>
+        <v>39.454545454545453</v>
       </c>
       <c r="V18" s="88">
         <f t="shared" si="8"/>
-        <v>0.95454545454545447</v>
+        <v>0.98636363636363633</v>
       </c>
       <c r="W18" s="89">
         <f t="shared" si="9"/>
-        <v>-1.8181818181818201</v>
+        <v>-0.54545454545454675</v>
       </c>
       <c r="X18" s="89">
         <f t="shared" si="10"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Y18" s="89">
         <f t="shared" si="11"/>
-        <v>-20.90909090909091</v>
+        <v>-20.272727272727273</v>
       </c>
       <c r="Z18" s="90">
         <f t="shared" si="12"/>
-        <v>216507272.72727272</v>
+        <v>223724181.81818181</v>
       </c>
       <c r="AA18" s="90">
         <f t="shared" si="13"/>
-        <v>-3492727.2727272809</v>
+        <v>3724181.8181818128</v>
       </c>
       <c r="AB18" s="91">
         <f t="shared" si="14"/>
-        <v>0.98412396694214876</v>
+        <v>1.0169280991735536</v>
       </c>
       <c r="AC18" s="92">
         <f t="shared" si="15"/>
-        <v>1.368421052631579</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" s="93">
         <f t="shared" si="16"/>
-        <v>7400736.8421052629</v>
+        <v>7030700</v>
       </c>
       <c r="AE18" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C18),0)</f>
@@ -16075,15 +16075,15 @@
       </c>
       <c r="AN18" s="81">
         <f t="shared" si="22"/>
-        <v>38.18181818181818</v>
+        <v>39.454545454545453</v>
       </c>
       <c r="AO18" s="81">
         <f t="shared" si="23"/>
-        <v>-5.8181818181818201</v>
+        <v>-4.5454545454545467</v>
       </c>
       <c r="AP18" s="83">
         <f t="shared" si="24"/>
-        <v>-0.13223140495867772</v>
+        <v>-0.10330578512396697</v>
       </c>
       <c r="AQ18" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C18,"Segment Price","3mio&gt;"),0)</f>
@@ -16271,43 +16271,43 @@
       </c>
       <c r="U19" s="87">
         <f t="shared" si="7"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="V19" s="88">
         <f t="shared" si="8"/>
-        <v>0.81818181818181823</v>
+        <v>0.84545454545454557</v>
       </c>
       <c r="W19" s="89">
         <f t="shared" si="9"/>
-        <v>-10.909090909090907</v>
+        <v>-9.2727272727272663</v>
       </c>
       <c r="X19" s="89">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y19" s="89">
         <f t="shared" si="11"/>
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="Z19" s="90">
         <f t="shared" si="12"/>
-        <v>251405454.54545456</v>
+        <v>259785636.36363637</v>
       </c>
       <c r="AA19" s="90">
         <f t="shared" si="13"/>
-        <v>-78594545.454545438</v>
+        <v>-70214363.636363626</v>
       </c>
       <c r="AB19" s="91">
         <f t="shared" si="14"/>
-        <v>0.76183471074380171</v>
+        <v>0.7872292011019284</v>
       </c>
       <c r="AC19" s="92">
         <f t="shared" si="15"/>
-        <v>2.2105263157894739</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" s="93">
         <f t="shared" si="16"/>
-        <v>12516736.842105264</v>
+        <v>11890900</v>
       </c>
       <c r="AE19" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C19),0)</f>
@@ -16347,15 +16347,15 @@
       </c>
       <c r="AN19" s="81">
         <f t="shared" si="22"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="AO19" s="81">
         <f t="shared" si="23"/>
-        <v>-4.9090909090909065</v>
+        <v>-3.2727272727272663</v>
       </c>
       <c r="AP19" s="83">
         <f t="shared" si="24"/>
-        <v>-9.0909090909090856E-2</v>
+        <v>-6.060606060606049E-2</v>
       </c>
       <c r="AQ19" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C19,"Segment Price","3mio&gt;"),0)</f>
@@ -16543,43 +16543,43 @@
       </c>
       <c r="U20" s="87">
         <f t="shared" si="7"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="V20" s="88">
         <f t="shared" si="8"/>
-        <v>0.61363636363636365</v>
+        <v>0.63409090909090915</v>
       </c>
       <c r="W20" s="89">
         <f t="shared" si="9"/>
-        <v>-30.909090909090907</v>
+        <v>-29.272727272727266</v>
       </c>
       <c r="X20" s="89">
         <f t="shared" si="10"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Y20" s="89">
         <f t="shared" si="11"/>
-        <v>-60.909090909090907</v>
+        <v>-60.272727272727273</v>
       </c>
       <c r="Z20" s="90">
         <f t="shared" si="12"/>
-        <v>170950909.09090909</v>
+        <v>176649272.72727275</v>
       </c>
       <c r="AA20" s="90">
         <f t="shared" si="13"/>
-        <v>80950909.090909094</v>
+        <v>86649272.727272749</v>
       </c>
       <c r="AB20" s="91">
         <f t="shared" si="14"/>
-        <v>1.8994545454545455</v>
+        <v>1.9627696969696973</v>
       </c>
       <c r="AC20" s="92">
         <f t="shared" si="15"/>
-        <v>3.263157894736842</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" s="93">
         <f t="shared" si="16"/>
-        <v>1437789.4736842106</v>
+        <v>1365900</v>
       </c>
       <c r="AE20" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C20),0)</f>
@@ -16619,15 +16619,15 @@
       </c>
       <c r="AN20" s="81">
         <f t="shared" si="22"/>
-        <v>49.090909090909093</v>
+        <v>50.727272727272734</v>
       </c>
       <c r="AO20" s="81">
         <f t="shared" si="23"/>
-        <v>-14.909090909090907</v>
+        <v>-13.272727272727266</v>
       </c>
       <c r="AP20" s="83">
         <f t="shared" si="24"/>
-        <v>-0.23295454545454541</v>
+        <v>-0.20738636363636354</v>
       </c>
       <c r="AQ20" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C20,"Segment Price","3mio&gt;"),0)</f>
@@ -16667,11 +16667,11 @@
       </c>
       <c r="AZ20" s="85">
         <f t="shared" si="31"/>
-        <v>3482333.333333333</v>
+        <v>3482333.3333333335</v>
       </c>
       <c r="BA20" s="85">
         <f t="shared" si="32"/>
-        <v>-4062500</v>
+        <v>-4062499.9999999995</v>
       </c>
       <c r="BB20" s="95">
         <f t="shared" si="33"/>
@@ -16815,43 +16815,43 @@
       </c>
       <c r="U21" s="87">
         <f t="shared" si="7"/>
-        <v>35.454545454545453</v>
+        <v>36.63636363636364</v>
       </c>
       <c r="V21" s="88">
         <f t="shared" si="8"/>
-        <v>1.7727272727272727</v>
+        <v>1.831818181818182</v>
       </c>
       <c r="W21" s="89">
         <f t="shared" si="9"/>
-        <v>15.454545454545453</v>
+        <v>16.63636363636364</v>
       </c>
       <c r="X21" s="89">
         <f t="shared" si="10"/>
-        <v>24.545454545454547</v>
+        <v>25.363636363636367</v>
       </c>
       <c r="Y21" s="89">
         <f t="shared" si="11"/>
-        <v>4.5454545454545467</v>
+        <v>5.3636363636363669</v>
       </c>
       <c r="Z21" s="90">
         <f t="shared" si="12"/>
-        <v>169328181.81818181</v>
+        <v>174972454.54545456</v>
       </c>
       <c r="AA21" s="90">
         <f t="shared" si="13"/>
-        <v>-270671818.18181819</v>
+        <v>-265027545.45454544</v>
       </c>
       <c r="AB21" s="91">
         <f t="shared" si="14"/>
-        <v>0.38483677685950413</v>
+        <v>0.39766466942148765</v>
       </c>
       <c r="AC21" s="92">
         <f t="shared" si="15"/>
-        <v>0.36842105263157893</v>
+        <v>0.35</v>
       </c>
       <c r="AD21" s="93">
         <f t="shared" si="16"/>
-        <v>19890157.894736841</v>
+        <v>18895650</v>
       </c>
       <c r="AE21" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C21),0)</f>
@@ -16891,15 +16891,15 @@
       </c>
       <c r="AN21" s="81">
         <f t="shared" si="22"/>
-        <v>35.454545454545453</v>
+        <v>36.63636363636364</v>
       </c>
       <c r="AO21" s="81">
         <f t="shared" si="23"/>
-        <v>-1.5454545454545467</v>
+        <v>-0.36363636363635976</v>
       </c>
       <c r="AP21" s="83">
         <f t="shared" si="24"/>
-        <v>-4.1769041769041802E-2</v>
+        <v>-9.8280098280097237E-3</v>
       </c>
       <c r="AQ21" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C21,"Segment Price","3mio&gt;"),0)</f>
@@ -17087,43 +17087,43 @@
       </c>
       <c r="U22" s="87">
         <f t="shared" si="7"/>
-        <v>51.81818181818182</v>
+        <v>53.545454545454547</v>
       </c>
       <c r="V22" s="88">
         <f t="shared" si="8"/>
-        <v>1.7272727272727273</v>
+        <v>1.7848484848484849</v>
       </c>
       <c r="W22" s="89">
         <f t="shared" si="9"/>
-        <v>21.81818181818182</v>
+        <v>23.545454545454547</v>
       </c>
       <c r="X22" s="89">
         <f t="shared" si="10"/>
-        <v>13.636363636363637</v>
+        <v>14.09090909090909</v>
       </c>
       <c r="Y22" s="89">
         <f t="shared" si="11"/>
-        <v>-16.363636363636363</v>
+        <v>-15.90909090909091</v>
       </c>
       <c r="Z22" s="90">
         <f t="shared" si="12"/>
-        <v>181311818.18181819</v>
+        <v>187355545.45454544</v>
       </c>
       <c r="AA22" s="90">
         <f t="shared" si="13"/>
-        <v>16311818.181818187</v>
+        <v>22355545.454545438</v>
       </c>
       <c r="AB22" s="91">
         <f t="shared" si="14"/>
-        <v>1.0988595041322315</v>
+        <v>1.1354881542699724</v>
       </c>
       <c r="AC22" s="92">
         <f t="shared" si="15"/>
-        <v>0.57894736842105265</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AD22" s="93">
         <f t="shared" si="16"/>
-        <v>5185210.5263157897</v>
+        <v>4925950</v>
       </c>
       <c r="AE22" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C22),0)</f>
@@ -17163,15 +17163,15 @@
       </c>
       <c r="AN22" s="81">
         <f t="shared" si="22"/>
-        <v>51.81818181818182</v>
+        <v>53.545454545454547</v>
       </c>
       <c r="AO22" s="81">
         <f t="shared" si="23"/>
-        <v>43.81818181818182</v>
+        <v>45.545454545454547</v>
       </c>
       <c r="AP22" s="83">
         <f t="shared" si="24"/>
-        <v>5.4772727272727275</v>
+        <v>5.6931818181818183</v>
       </c>
       <c r="AQ22" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C22,"Segment Price","3mio&gt;"),0)</f>
@@ -17211,11 +17211,11 @@
       </c>
       <c r="AZ22" s="85">
         <f t="shared" si="31"/>
-        <v>3499000</v>
+        <v>3498999.9999999995</v>
       </c>
       <c r="BA22" s="85">
         <f t="shared" si="32"/>
-        <v>3499000</v>
+        <v>3498999.9999999995</v>
       </c>
       <c r="BB22" s="95">
         <f t="shared" si="33"/>
@@ -17359,43 +17359,43 @@
       </c>
       <c r="U23" s="87">
         <f t="shared" si="7"/>
-        <v>111.81818181818181</v>
+        <v>115.54545454545453</v>
       </c>
       <c r="V23" s="88">
         <f t="shared" si="8"/>
-        <v>0.93181818181818177</v>
+        <v>0.96287878787878778</v>
       </c>
       <c r="W23" s="89">
         <f t="shared" si="9"/>
-        <v>-8.181818181818187</v>
+        <v>-4.4545454545454675</v>
       </c>
       <c r="X23" s="89">
         <f t="shared" si="10"/>
-        <v>40.909090909090907</v>
+        <v>42.272727272727266</v>
       </c>
       <c r="Y23" s="89">
         <f t="shared" si="11"/>
-        <v>-79.090909090909093</v>
+        <v>-77.727272727272734</v>
       </c>
       <c r="Z23" s="90">
         <f t="shared" si="12"/>
-        <v>412797272.72727275</v>
+        <v>426557181.81818187</v>
       </c>
       <c r="AA23" s="90">
         <f t="shared" si="13"/>
-        <v>-211202727.27272725</v>
+        <v>-197442818.18181813</v>
       </c>
       <c r="AB23" s="91">
         <f t="shared" si="14"/>
-        <v>0.66153409090909099</v>
+        <v>0.68358522727272741</v>
       </c>
       <c r="AC23" s="92">
         <f t="shared" si="15"/>
-        <v>4.1578947368421053</v>
+        <v>3.95</v>
       </c>
       <c r="AD23" s="93">
         <f t="shared" si="16"/>
-        <v>24875842.105263159</v>
+        <v>23632050</v>
       </c>
       <c r="AE23" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C23),0)</f>
@@ -17435,15 +17435,15 @@
       </c>
       <c r="AN23" s="81">
         <f t="shared" si="22"/>
-        <v>111.81818181818181</v>
+        <v>115.54545454545453</v>
       </c>
       <c r="AO23" s="81">
         <f t="shared" si="23"/>
-        <v>-17.181818181818187</v>
+        <v>-13.454545454545467</v>
       </c>
       <c r="AP23" s="83">
         <f t="shared" si="24"/>
-        <v>-0.13319238900634253</v>
+        <v>-0.10429880197322068</v>
       </c>
       <c r="AQ23" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C23,"Segment Price","3mio&gt;"),0)</f>
@@ -17483,15 +17483,15 @@
       </c>
       <c r="AZ23" s="85">
         <f t="shared" si="31"/>
-        <v>3691682.9268292687</v>
+        <v>3691682.9268292692</v>
       </c>
       <c r="BA23" s="85">
         <f t="shared" si="32"/>
-        <v>-2589317.0731707313</v>
+        <v>-2589317.0731707308</v>
       </c>
       <c r="BB23" s="95">
         <f t="shared" si="33"/>
-        <v>-0.41224599158903541</v>
+        <v>-0.4122459915890353</v>
       </c>
       <c r="BC23" s="78">
         <f>IFERROR(VLOOKUP(C23,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -17631,43 +17631,43 @@
       </c>
       <c r="U24" s="87">
         <f t="shared" si="7"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="V24" s="88">
         <f t="shared" si="8"/>
-        <v>0.81818181818181812</v>
+        <v>0.84545454545454535</v>
       </c>
       <c r="W24" s="89">
         <f t="shared" si="9"/>
-        <v>-3.6363636363636367</v>
+        <v>-3.0909090909090935</v>
       </c>
       <c r="X24" s="89">
         <f t="shared" si="10"/>
-        <v>5.454545454545455</v>
+        <v>5.6363636363636367</v>
       </c>
       <c r="Y24" s="89">
         <f t="shared" si="11"/>
-        <v>-14.545454545454545</v>
+        <v>-14.363636363636363</v>
       </c>
       <c r="Z24" s="90">
         <f t="shared" si="12"/>
-        <v>51529090.909090906</v>
+        <v>53246727.272727266</v>
       </c>
       <c r="AA24" s="90">
         <f t="shared" si="13"/>
-        <v>-48470909.090909094</v>
+        <v>-46753272.727272734</v>
       </c>
       <c r="AB24" s="91">
         <f t="shared" si="14"/>
-        <v>0.51529090909090902</v>
+        <v>0.53246727272727268</v>
       </c>
       <c r="AC24" s="92">
         <f t="shared" si="15"/>
-        <v>0.73684210526315785</v>
+        <v>0.7</v>
       </c>
       <c r="AD24" s="93">
         <f t="shared" si="16"/>
-        <v>4268736.8421052629</v>
+        <v>4055300</v>
       </c>
       <c r="AE24" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C24),0)</f>
@@ -17707,15 +17707,15 @@
       </c>
       <c r="AN24" s="81">
         <f t="shared" si="22"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="AO24" s="81">
         <f t="shared" si="23"/>
-        <v>-14.636363636363637</v>
+        <v>-14.090909090909093</v>
       </c>
       <c r="AP24" s="83">
         <f t="shared" si="24"/>
-        <v>-0.47214076246334313</v>
+        <v>-0.45454545454545464</v>
       </c>
       <c r="AQ24" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C24,"Segment Price","3mio&gt;"),0)</f>
@@ -17903,43 +17903,43 @@
       </c>
       <c r="U25" s="87">
         <f t="shared" si="7"/>
-        <v>76.36363636363636</v>
+        <v>78.909090909090907</v>
       </c>
       <c r="V25" s="88">
         <f t="shared" si="8"/>
-        <v>0.95454545454545447</v>
+        <v>0.98636363636363633</v>
       </c>
       <c r="W25" s="89">
         <f t="shared" si="9"/>
-        <v>-3.6363636363636402</v>
+        <v>-1.0909090909090935</v>
       </c>
       <c r="X25" s="89">
         <f t="shared" si="10"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="Y25" s="89">
         <f t="shared" si="11"/>
-        <v>-63.63636363636364</v>
+        <v>-63.090909090909093</v>
       </c>
       <c r="Z25" s="90">
         <f t="shared" si="12"/>
-        <v>245105454.54545456</v>
+        <v>253275636.36363637</v>
       </c>
       <c r="AA25" s="90">
         <f t="shared" si="13"/>
-        <v>-98894545.454545438</v>
+        <v>-90724363.636363626</v>
       </c>
       <c r="AB25" s="91">
         <f t="shared" si="14"/>
-        <v>0.71251585623678648</v>
+        <v>0.73626638477801276</v>
       </c>
       <c r="AC25" s="92">
         <f t="shared" si="15"/>
-        <v>2.736842105263158</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" s="93">
         <f t="shared" si="16"/>
-        <v>13375157.894736841</v>
+        <v>12706400</v>
       </c>
       <c r="AE25" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C25),0)</f>
@@ -17979,15 +17979,15 @@
       </c>
       <c r="AN25" s="81">
         <f t="shared" si="22"/>
-        <v>76.36363636363636</v>
+        <v>78.909090909090907</v>
       </c>
       <c r="AO25" s="81">
         <f t="shared" si="23"/>
-        <v>-12.63636363636364</v>
+        <v>-10.090909090909093</v>
       </c>
       <c r="AP25" s="83">
         <f t="shared" si="24"/>
-        <v>-0.14198161389172628</v>
+        <v>-0.11338100102145049</v>
       </c>
       <c r="AQ25" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C25,"Segment Price","3mio&gt;"),0)</f>
@@ -18175,43 +18175,43 @@
       </c>
       <c r="U26" s="87">
         <f t="shared" si="7"/>
-        <v>98.181818181818187</v>
+        <v>101.45454545454547</v>
       </c>
       <c r="V26" s="88">
         <f t="shared" si="8"/>
-        <v>0.98181818181818192</v>
+        <v>1.0145454545454546</v>
       </c>
       <c r="W26" s="89">
         <f t="shared" si="9"/>
-        <v>-1.818181818181813</v>
+        <v>1.4545454545454675</v>
       </c>
       <c r="X26" s="89">
         <f t="shared" si="10"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="Y26" s="89">
         <f t="shared" si="11"/>
-        <v>-56.36363636363636</v>
+        <v>-54.909090909090907</v>
       </c>
       <c r="Z26" s="90">
         <f t="shared" si="12"/>
-        <v>388810909.09090912</v>
+        <v>401771272.72727275</v>
       </c>
       <c r="AA26" s="90">
         <f t="shared" si="13"/>
-        <v>-41189090.909090877</v>
+        <v>-28228727.272727251</v>
       </c>
       <c r="AB26" s="91">
         <f t="shared" si="14"/>
-        <v>0.90421141649048631</v>
+        <v>0.93435179704016913</v>
       </c>
       <c r="AC26" s="92">
         <f t="shared" si="15"/>
-        <v>3.3684210526315788</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" s="93">
         <f t="shared" si="16"/>
-        <v>15128210.52631579</v>
+        <v>14371800</v>
       </c>
       <c r="AE26" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C26),0)</f>
@@ -18251,15 +18251,15 @@
       </c>
       <c r="AN26" s="81">
         <f t="shared" si="22"/>
-        <v>98.181818181818187</v>
+        <v>101.45454545454547</v>
       </c>
       <c r="AO26" s="81">
         <f t="shared" si="23"/>
-        <v>-6.818181818181813</v>
+        <v>-3.5454545454545325</v>
       </c>
       <c r="AP26" s="83">
         <f t="shared" si="24"/>
-        <v>-6.4935064935064887E-2</v>
+        <v>-3.3766233766233646E-2</v>
       </c>
       <c r="AQ26" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C26,"Segment Price","3mio&gt;"),0)</f>
@@ -18447,43 +18447,43 @@
       </c>
       <c r="U27" s="87">
         <f t="shared" si="7"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="V27" s="88">
         <f t="shared" si="8"/>
-        <v>0.54545454545454541</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="W27" s="89">
         <f t="shared" si="9"/>
-        <v>-13.636363636363637</v>
+        <v>-13.090909090909093</v>
       </c>
       <c r="X27" s="89">
         <f t="shared" si="10"/>
-        <v>2.7272727272727275</v>
+        <v>2.8181818181818183</v>
       </c>
       <c r="Y27" s="89">
         <f t="shared" si="11"/>
-        <v>-27.272727272727273</v>
+        <v>-27.18181818181818</v>
       </c>
       <c r="Z27" s="90">
         <f t="shared" si="12"/>
-        <v>45529090.909090906</v>
+        <v>47046727.272727266</v>
       </c>
       <c r="AA27" s="90">
         <f t="shared" si="13"/>
-        <v>-83470909.090909094</v>
+        <v>-81953272.727272734</v>
       </c>
       <c r="AB27" s="91">
         <f t="shared" si="14"/>
-        <v>0.35293868921775895</v>
+        <v>0.36470331219168423</v>
       </c>
       <c r="AC27" s="92">
         <f t="shared" si="15"/>
-        <v>1.263157894736842</v>
+        <v>1.2</v>
       </c>
       <c r="AD27" s="93">
         <f t="shared" si="16"/>
-        <v>5910842.1052631577</v>
+        <v>5615300</v>
       </c>
       <c r="AE27" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C27),0)</f>
@@ -18523,15 +18523,15 @@
       </c>
       <c r="AN27" s="81">
         <f t="shared" si="22"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="AO27" s="81">
         <f t="shared" si="23"/>
-        <v>-4.6363636363636367</v>
+        <v>-4.0909090909090935</v>
       </c>
       <c r="AP27" s="83">
         <f t="shared" si="24"/>
-        <v>-0.2207792207792208</v>
+        <v>-0.19480519480519493</v>
       </c>
       <c r="AQ27" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C27,"Segment Price","3mio&gt;"),0)</f>
@@ -18571,15 +18571,15 @@
       </c>
       <c r="AZ27" s="85">
         <f t="shared" si="31"/>
-        <v>2782333.333333333</v>
+        <v>2782333.3333333335</v>
       </c>
       <c r="BA27" s="85">
         <f t="shared" si="32"/>
-        <v>-750000.00000000047</v>
+        <v>-750000</v>
       </c>
       <c r="BB27" s="95">
         <f t="shared" si="33"/>
-        <v>-0.21232424271020112</v>
+        <v>-0.21232424271020098</v>
       </c>
       <c r="BC27" s="78">
         <f>IFERROR(VLOOKUP(C27,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -18719,43 +18719,43 @@
       </c>
       <c r="U28" s="87">
         <f t="shared" si="7"/>
-        <v>117.27272727272728</v>
+        <v>121.18181818181819</v>
       </c>
       <c r="V28" s="88">
         <f t="shared" si="8"/>
-        <v>1.3030303030303032</v>
+        <v>1.3464646464646466</v>
       </c>
       <c r="W28" s="89">
         <f t="shared" si="9"/>
-        <v>27.27272727272728</v>
+        <v>31.181818181818187</v>
       </c>
       <c r="X28" s="89">
         <f t="shared" si="10"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="Y28" s="89">
         <f t="shared" si="11"/>
-        <v>-46.36363636363636</v>
+        <v>-44.909090909090907</v>
       </c>
       <c r="Z28" s="90">
         <f t="shared" si="12"/>
-        <v>413064545.45454544</v>
+        <v>426833363.63636363</v>
       </c>
       <c r="AA28" s="90">
         <f t="shared" si="13"/>
-        <v>26064545.454545438</v>
+        <v>39833363.636363626</v>
       </c>
       <c r="AB28" s="91">
         <f t="shared" si="14"/>
-        <v>1.0673502466525722</v>
+        <v>1.102928588207658</v>
       </c>
       <c r="AC28" s="92">
         <f t="shared" si="15"/>
-        <v>2.4736842105263159</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" s="93">
         <f t="shared" si="16"/>
-        <v>12397000</v>
+        <v>11777150</v>
       </c>
       <c r="AE28" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C28),0)</f>
@@ -18795,15 +18795,15 @@
       </c>
       <c r="AN28" s="81">
         <f t="shared" si="22"/>
-        <v>117.27272727272728</v>
+        <v>121.18181818181819</v>
       </c>
       <c r="AO28" s="81">
         <f t="shared" si="23"/>
-        <v>23.27272727272728</v>
+        <v>27.181818181818187</v>
       </c>
       <c r="AP28" s="83">
         <f t="shared" si="24"/>
-        <v>0.24758220502901362</v>
+        <v>0.28916827852998073</v>
       </c>
       <c r="AQ28" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C28,"Segment Price","3mio&gt;"),0)</f>
@@ -18991,43 +18991,43 @@
       </c>
       <c r="U29" s="87">
         <f t="shared" si="7"/>
-        <v>109.09090909090909</v>
+        <v>112.72727272727272</v>
       </c>
       <c r="V29" s="88">
         <f t="shared" si="8"/>
-        <v>1.2121212121212122</v>
+        <v>1.2525252525252524</v>
       </c>
       <c r="W29" s="89">
         <f t="shared" si="9"/>
-        <v>19.090909090909093</v>
+        <v>22.72727272727272</v>
       </c>
       <c r="X29" s="89">
         <f t="shared" si="10"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Y29" s="89">
         <f t="shared" si="11"/>
-        <v>-70.909090909090907</v>
+        <v>-70.27272727272728</v>
       </c>
       <c r="Z29" s="90">
         <f t="shared" si="12"/>
-        <v>329618181.81818181</v>
+        <v>340605454.5454545</v>
       </c>
       <c r="AA29" s="90">
         <f t="shared" si="13"/>
-        <v>-57381818.181818187</v>
+        <v>-46394545.454545498</v>
       </c>
       <c r="AB29" s="91">
         <f t="shared" si="14"/>
-        <v>0.85172656800563773</v>
+        <v>0.88011745360582561</v>
       </c>
       <c r="AC29" s="92">
         <f t="shared" si="15"/>
-        <v>2.6315789473684212</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" s="93">
         <f t="shared" si="16"/>
-        <v>14007368.421052631</v>
+        <v>13307000</v>
       </c>
       <c r="AE29" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C29),0)</f>
@@ -19067,15 +19067,15 @@
       </c>
       <c r="AN29" s="81">
         <f t="shared" si="22"/>
-        <v>109.09090909090909</v>
+        <v>112.72727272727272</v>
       </c>
       <c r="AO29" s="81">
         <f t="shared" si="23"/>
-        <v>15.090909090909093</v>
+        <v>18.72727272727272</v>
       </c>
       <c r="AP29" s="83">
         <f t="shared" si="24"/>
-        <v>0.160541586073501</v>
+        <v>0.19922630560928425</v>
       </c>
       <c r="AQ29" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C29,"Segment Price","3mio&gt;"),0)</f>
@@ -19263,43 +19263,43 @@
       </c>
       <c r="U30" s="87">
         <f t="shared" si="7"/>
-        <v>92.72727272727272</v>
+        <v>95.818181818181813</v>
       </c>
       <c r="V30" s="88">
         <f t="shared" si="8"/>
-        <v>1.0303030303030303</v>
+        <v>1.0646464646464646</v>
       </c>
       <c r="W30" s="89">
         <f t="shared" si="9"/>
-        <v>2.7272727272727195</v>
+        <v>5.818181818181813</v>
       </c>
       <c r="X30" s="89">
         <f t="shared" si="10"/>
-        <v>46.36363636363636</v>
+        <v>47.909090909090907</v>
       </c>
       <c r="Y30" s="89">
         <f t="shared" si="11"/>
-        <v>-43.63636363636364</v>
+        <v>-42.090909090909093</v>
       </c>
       <c r="Z30" s="90">
         <f t="shared" si="12"/>
-        <v>405452727.27272725</v>
+        <v>418967818.18181813</v>
       </c>
       <c r="AA30" s="90">
         <f t="shared" si="13"/>
-        <v>18452727.272727251</v>
+        <v>31967818.181818128</v>
       </c>
       <c r="AB30" s="91">
         <f t="shared" si="14"/>
-        <v>1.0476814658210007</v>
+        <v>1.0826041813483673</v>
       </c>
       <c r="AC30" s="92">
         <f t="shared" si="15"/>
-        <v>2.9473684210526314</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" s="93">
         <f t="shared" si="16"/>
-        <v>12543894.736842105</v>
+        <v>11916700</v>
       </c>
       <c r="AE30" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C30),0)</f>
@@ -19339,15 +19339,15 @@
       </c>
       <c r="AN30" s="81">
         <f t="shared" si="22"/>
-        <v>92.72727272727272</v>
+        <v>95.818181818181813</v>
       </c>
       <c r="AO30" s="81">
         <f t="shared" si="23"/>
-        <v>-12.27272727272728</v>
+        <v>-9.181818181818187</v>
       </c>
       <c r="AP30" s="83">
         <f t="shared" si="24"/>
-        <v>-0.11688311688311696</v>
+        <v>-8.7445887445887494E-2</v>
       </c>
       <c r="AQ30" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C30,"Segment Price","3mio&gt;"),0)</f>
@@ -19535,43 +19535,43 @@
       </c>
       <c r="U31" s="87">
         <f t="shared" si="7"/>
-        <v>24.545454545454547</v>
+        <v>25.363636363636367</v>
       </c>
       <c r="V31" s="88">
         <f t="shared" si="8"/>
-        <v>0.81818181818181823</v>
+        <v>0.84545454545454557</v>
       </c>
       <c r="W31" s="89">
         <f t="shared" si="9"/>
-        <v>-5.4545454545454533</v>
+        <v>-4.6363636363636331</v>
       </c>
       <c r="X31" s="89">
         <f t="shared" si="10"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="Y31" s="89">
         <f t="shared" si="11"/>
-        <v>-13.636363636363637</v>
+        <v>-13.090909090909093</v>
       </c>
       <c r="Z31" s="90">
         <f t="shared" si="12"/>
-        <v>142884545.45454544</v>
+        <v>147647363.63636363</v>
       </c>
       <c r="AA31" s="90">
         <f t="shared" si="13"/>
-        <v>-7115454.5454545617</v>
+        <v>-2352636.3636363745</v>
       </c>
       <c r="AB31" s="91">
         <f t="shared" si="14"/>
-        <v>0.95256363636363628</v>
+        <v>0.98431575757575751</v>
       </c>
       <c r="AC31" s="92">
         <f t="shared" si="15"/>
-        <v>1.1052631578947369</v>
+        <v>1.05</v>
       </c>
       <c r="AD31" s="93">
         <f t="shared" si="16"/>
-        <v>5137315.7894736845</v>
+        <v>4880450</v>
       </c>
       <c r="AE31" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C31),0)</f>
@@ -19611,15 +19611,15 @@
       </c>
       <c r="AN31" s="81">
         <f t="shared" si="22"/>
-        <v>24.545454545454547</v>
+        <v>25.363636363636367</v>
       </c>
       <c r="AO31" s="81">
         <f t="shared" si="23"/>
-        <v>-5.4545454545454533</v>
+        <v>-4.6363636363636331</v>
       </c>
       <c r="AP31" s="83">
         <f t="shared" si="24"/>
-        <v>-0.18181818181818177</v>
+        <v>-0.15454545454545443</v>
       </c>
       <c r="AQ31" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C31,"Segment Price","3mio&gt;"),0)</f>
@@ -19807,43 +19807,43 @@
       </c>
       <c r="U32" s="87">
         <f t="shared" si="7"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="V32" s="88">
         <f t="shared" si="8"/>
-        <v>1.0909090909090911</v>
+        <v>1.1272727272727274</v>
       </c>
       <c r="W32" s="89">
         <f t="shared" si="9"/>
-        <v>3.6363636363636402</v>
+        <v>5.0909090909090935</v>
       </c>
       <c r="X32" s="89">
         <f t="shared" si="10"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="Y32" s="89">
         <f t="shared" si="11"/>
-        <v>-7.2727272727272734</v>
+        <v>-6.181818181818187</v>
       </c>
       <c r="Z32" s="90">
         <f t="shared" si="12"/>
-        <v>272138181.81818181</v>
+        <v>281209454.5454545</v>
       </c>
       <c r="AA32" s="90">
         <f t="shared" si="13"/>
-        <v>100138181.81818181</v>
+        <v>109209454.5454545</v>
       </c>
       <c r="AB32" s="91">
         <f t="shared" si="14"/>
-        <v>1.5821987315010571</v>
+        <v>1.6349386892177586</v>
       </c>
       <c r="AC32" s="92">
         <f t="shared" si="15"/>
-        <v>1.263157894736842</v>
+        <v>1.2</v>
       </c>
       <c r="AD32" s="93">
         <f t="shared" si="16"/>
-        <v>3800842.1052631577</v>
+        <v>3610800</v>
       </c>
       <c r="AE32" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C32),0)</f>
@@ -19883,15 +19883,15 @@
       </c>
       <c r="AN32" s="81">
         <f t="shared" si="22"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="AO32" s="81">
         <f t="shared" si="23"/>
-        <v>5.6363636363636402</v>
+        <v>7.0909090909090935</v>
       </c>
       <c r="AP32" s="83">
         <f t="shared" si="24"/>
-        <v>0.14832535885167475</v>
+        <v>0.18660287081339719</v>
       </c>
       <c r="AQ32" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C32,"Segment Price","3mio&gt;"),0)</f>
@@ -20079,43 +20079,43 @@
       </c>
       <c r="U33" s="87">
         <f t="shared" si="7"/>
-        <v>21.81818181818182</v>
+        <v>22.545454545454547</v>
       </c>
       <c r="V33" s="88">
         <f t="shared" si="8"/>
-        <v>0.72727272727272729</v>
+        <v>0.75151515151515158</v>
       </c>
       <c r="W33" s="89">
         <f t="shared" si="9"/>
-        <v>-8.1818181818181799</v>
+        <v>-7.4545454545454533</v>
       </c>
       <c r="X33" s="89">
         <f t="shared" si="10"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="Y33" s="89">
         <f t="shared" si="11"/>
-        <v>-13.636363636363637</v>
+        <v>-13.090909090909093</v>
       </c>
       <c r="Z33" s="90">
         <f t="shared" si="12"/>
-        <v>95160000</v>
+        <v>98332000</v>
       </c>
       <c r="AA33" s="90">
         <f t="shared" si="13"/>
-        <v>-54840000</v>
+        <v>-51668000</v>
       </c>
       <c r="AB33" s="91">
         <f t="shared" si="14"/>
-        <v>0.63439999999999996</v>
+        <v>0.65554666666666672</v>
       </c>
       <c r="AC33" s="92">
         <f t="shared" si="15"/>
-        <v>1.1578947368421053</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AD33" s="93">
         <f t="shared" si="16"/>
-        <v>6058315.7894736845</v>
+        <v>5755400</v>
       </c>
       <c r="AE33" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C33),0)</f>
@@ -20155,15 +20155,15 @@
       </c>
       <c r="AN33" s="81">
         <f t="shared" si="22"/>
-        <v>21.81818181818182</v>
+        <v>22.545454545454547</v>
       </c>
       <c r="AO33" s="81">
         <f t="shared" si="23"/>
-        <v>1.8181818181818201</v>
+        <v>2.5454545454545467</v>
       </c>
       <c r="AP33" s="83">
         <f t="shared" si="24"/>
-        <v>9.0909090909091009E-2</v>
+        <v>0.12727272727272734</v>
       </c>
       <c r="AQ33" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C33,"Segment Price","3mio&gt;"),0)</f>
@@ -20351,43 +20351,43 @@
       </c>
       <c r="U34" s="87">
         <f t="shared" si="7"/>
-        <v>21.81818181818182</v>
+        <v>22.545454545454547</v>
       </c>
       <c r="V34" s="88">
         <f t="shared" si="8"/>
-        <v>0.72727272727272729</v>
+        <v>0.75151515151515158</v>
       </c>
       <c r="W34" s="89">
         <f t="shared" si="9"/>
-        <v>-8.1818181818181799</v>
+        <v>-7.4545454545454533</v>
       </c>
       <c r="X34" s="89">
         <f t="shared" si="10"/>
-        <v>13.636363636363637</v>
+        <v>14.09090909090909</v>
       </c>
       <c r="Y34" s="89">
         <f t="shared" si="11"/>
-        <v>-16.363636363636363</v>
+        <v>-15.90909090909091</v>
       </c>
       <c r="Z34" s="90">
         <f t="shared" si="12"/>
-        <v>85614545.454545453</v>
+        <v>88468363.636363626</v>
       </c>
       <c r="AA34" s="90">
         <f t="shared" si="13"/>
-        <v>-64385454.545454547</v>
+        <v>-61531636.363636374</v>
       </c>
       <c r="AB34" s="91">
         <f t="shared" si="14"/>
-        <v>0.57076363636363636</v>
+        <v>0.58978909090909082</v>
       </c>
       <c r="AC34" s="92">
         <f t="shared" si="15"/>
-        <v>1.1578947368421053</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AD34" s="93">
         <f t="shared" si="16"/>
-        <v>6242526.3157894732</v>
+        <v>5930400</v>
       </c>
       <c r="AE34" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C34),0)</f>
@@ -20427,15 +20427,15 @@
       </c>
       <c r="AN34" s="81">
         <f t="shared" si="22"/>
-        <v>21.81818181818182</v>
+        <v>22.545454545454547</v>
       </c>
       <c r="AO34" s="81">
         <f t="shared" si="23"/>
-        <v>-18.18181818181818</v>
+        <v>-17.454545454545453</v>
       </c>
       <c r="AP34" s="83">
         <f t="shared" si="24"/>
-        <v>-0.45454545454545447</v>
+        <v>-0.43636363636363634</v>
       </c>
       <c r="AQ34" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C34,"Segment Price","3mio&gt;"),0)</f>
@@ -20475,15 +20475,15 @@
       </c>
       <c r="AZ34" s="85">
         <f t="shared" si="31"/>
-        <v>3923999.9999999995</v>
+        <v>3923999.9999999991</v>
       </c>
       <c r="BA34" s="85">
         <f t="shared" si="32"/>
-        <v>1624999.9999999995</v>
+        <v>1624999.9999999991</v>
       </c>
       <c r="BB34" s="95">
         <f t="shared" si="33"/>
-        <v>0.7068290561113526</v>
+        <v>0.70682905611135238</v>
       </c>
       <c r="BC34" s="78">
         <f>IFERROR(VLOOKUP(C34,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -20623,43 +20623,43 @@
       </c>
       <c r="U35" s="87">
         <f t="shared" si="7"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="V35" s="88">
         <f t="shared" si="8"/>
-        <v>0.63636363636363635</v>
+        <v>0.65757575757575759</v>
       </c>
       <c r="W35" s="89">
         <f t="shared" si="9"/>
-        <v>-10.90909090909091</v>
+        <v>-10.272727272727273</v>
       </c>
       <c r="X35" s="89">
         <f t="shared" si="10"/>
-        <v>5.454545454545455</v>
+        <v>5.6363636363636367</v>
       </c>
       <c r="Y35" s="89">
         <f t="shared" si="11"/>
-        <v>-24.545454545454547</v>
+        <v>-24.363636363636363</v>
       </c>
       <c r="Z35" s="90">
         <f t="shared" si="12"/>
-        <v>57799090.909090906</v>
+        <v>59725727.272727266</v>
       </c>
       <c r="AA35" s="90">
         <f t="shared" si="13"/>
-        <v>-107200909.09090909</v>
+        <v>-105274272.72727273</v>
       </c>
       <c r="AB35" s="91">
         <f t="shared" si="14"/>
-        <v>0.35029752066115699</v>
+        <v>0.36197410468319557</v>
       </c>
       <c r="AC35" s="92">
         <f t="shared" si="15"/>
-        <v>1.2105263157894737</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AD35" s="93">
         <f t="shared" si="16"/>
-        <v>7568789.4736842103</v>
+        <v>7190350</v>
       </c>
       <c r="AE35" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C35),0)</f>
@@ -20699,15 +20699,15 @@
       </c>
       <c r="AN35" s="81">
         <f t="shared" si="22"/>
-        <v>19.09090909090909</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="AO35" s="81">
         <f t="shared" si="23"/>
-        <v>-0.90909090909091006</v>
+        <v>-0.27272727272727337</v>
       </c>
       <c r="AP35" s="83">
         <f t="shared" si="24"/>
-        <v>-4.5454545454545504E-2</v>
+        <v>-1.3636363636363669E-2</v>
       </c>
       <c r="AQ35" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C35,"Segment Price","3mio&gt;"),0)</f>
@@ -20747,15 +20747,15 @@
       </c>
       <c r="AZ35" s="85">
         <f t="shared" si="31"/>
-        <v>3027571.4285714286</v>
+        <v>3027571.4285714282</v>
       </c>
       <c r="BA35" s="85">
         <f t="shared" si="32"/>
-        <v>-3486813.1868131864</v>
+        <v>-3486813.1868131869</v>
       </c>
       <c r="BB35" s="95">
         <f t="shared" si="33"/>
-        <v>-0.53524828401728042</v>
+        <v>-0.53524828401728053</v>
       </c>
       <c r="BC35" s="78">
         <f>IFERROR(VLOOKUP(C35,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -20895,43 +20895,43 @@
       </c>
       <c r="U36" s="87">
         <f t="shared" si="7"/>
-        <v>27.272727272727273</v>
+        <v>28.18181818181818</v>
       </c>
       <c r="V36" s="88">
         <f t="shared" si="8"/>
-        <v>0.90909090909090906</v>
+        <v>0.93939393939393934</v>
       </c>
       <c r="W36" s="89">
         <f t="shared" si="9"/>
-        <v>-2.7272727272727266</v>
+        <v>-1.8181818181818201</v>
       </c>
       <c r="X36" s="89">
         <f t="shared" si="10"/>
-        <v>10.90909090909091</v>
+        <v>11.272727272727273</v>
       </c>
       <c r="Y36" s="89">
         <f t="shared" si="11"/>
-        <v>-19.09090909090909</v>
+        <v>-18.727272727272727</v>
       </c>
       <c r="Z36" s="90">
         <f t="shared" si="12"/>
-        <v>107427272.72727272</v>
+        <v>111008181.81818181</v>
       </c>
       <c r="AA36" s="90">
         <f t="shared" si="13"/>
-        <v>-57572727.272727281</v>
+        <v>-53991818.181818187</v>
       </c>
       <c r="AB36" s="91">
         <f t="shared" si="14"/>
-        <v>0.65107438016528918</v>
+        <v>0.67277685950413224</v>
       </c>
       <c r="AC36" s="92">
         <f t="shared" si="15"/>
-        <v>1.0526315789473684</v>
+        <v>1</v>
       </c>
       <c r="AD36" s="93">
         <f t="shared" si="16"/>
-        <v>6611052.6315789474</v>
+        <v>6280500</v>
       </c>
       <c r="AE36" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C36),0)</f>
@@ -20971,15 +20971,15 @@
       </c>
       <c r="AN36" s="81">
         <f t="shared" si="22"/>
-        <v>27.272727272727273</v>
+        <v>28.18181818181818</v>
       </c>
       <c r="AO36" s="81">
         <f t="shared" si="23"/>
-        <v>-2.7272727272727266</v>
+        <v>-1.8181818181818201</v>
       </c>
       <c r="AP36" s="83">
         <f t="shared" si="24"/>
-        <v>-9.0909090909090884E-2</v>
+        <v>-6.060606060606067E-2</v>
       </c>
       <c r="AQ36" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C36,"Segment Price","3mio&gt;"),0)</f>
@@ -21019,15 +21019,15 @@
       </c>
       <c r="AZ36" s="85">
         <f t="shared" si="31"/>
-        <v>3938999.9999999995</v>
+        <v>3939000</v>
       </c>
       <c r="BA36" s="85">
         <f t="shared" si="32"/>
-        <v>-1035000.0000000005</v>
+        <v>-1035000</v>
       </c>
       <c r="BB36" s="95">
         <f t="shared" si="33"/>
-        <v>-0.20808202653799768</v>
+        <v>-0.20808202653799759</v>
       </c>
       <c r="BC36" s="78">
         <f>IFERROR(VLOOKUP(C36,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -21167,43 +21167,43 @@
       </c>
       <c r="U37" s="87">
         <f t="shared" si="7"/>
-        <v>46.36363636363636</v>
+        <v>47.909090909090907</v>
       </c>
       <c r="V37" s="88">
         <f t="shared" si="8"/>
-        <v>0.92727272727272725</v>
+        <v>0.95818181818181813</v>
       </c>
       <c r="W37" s="89">
         <f t="shared" si="9"/>
-        <v>-3.6363636363636402</v>
+        <v>-2.0909090909090935</v>
       </c>
       <c r="X37" s="89">
         <f t="shared" si="10"/>
-        <v>16.363636363636363</v>
+        <v>16.909090909090907</v>
       </c>
       <c r="Y37" s="89">
         <f t="shared" si="11"/>
-        <v>-33.63636363636364</v>
+        <v>-33.090909090909093</v>
       </c>
       <c r="Z37" s="90">
         <f t="shared" si="12"/>
-        <v>146953636.36363637</v>
+        <v>151852090.90909094</v>
       </c>
       <c r="AA37" s="90">
         <f t="shared" si="13"/>
-        <v>-68046363.636363626</v>
+        <v>-63147909.090909064</v>
       </c>
       <c r="AB37" s="91">
         <f t="shared" si="14"/>
-        <v>0.68350528541226219</v>
+        <v>0.70628879492600438</v>
       </c>
       <c r="AC37" s="92">
         <f t="shared" si="15"/>
-        <v>1.736842105263158</v>
+        <v>1.65</v>
       </c>
       <c r="AD37" s="93">
         <f t="shared" si="16"/>
-        <v>8479842.1052631587</v>
+        <v>8055850</v>
       </c>
       <c r="AE37" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C37),0)</f>
@@ -21243,15 +21243,15 @@
       </c>
       <c r="AN37" s="81">
         <f t="shared" si="22"/>
-        <v>46.36363636363636</v>
+        <v>47.909090909090907</v>
       </c>
       <c r="AO37" s="81">
         <f t="shared" si="23"/>
-        <v>-6.6363636363636402</v>
+        <v>-5.0909090909090935</v>
       </c>
       <c r="AP37" s="83">
         <f t="shared" si="24"/>
-        <v>-0.12521440823327623</v>
+        <v>-9.6054888507718747E-2</v>
       </c>
       <c r="AQ37" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C37,"Segment Price","3mio&gt;"),0)</f>
@@ -21291,15 +21291,15 @@
       </c>
       <c r="AZ37" s="85">
         <f t="shared" si="31"/>
-        <v>3169588.2352941181</v>
+        <v>3169588.2352941185</v>
       </c>
       <c r="BA37" s="85">
         <f t="shared" si="32"/>
-        <v>-4822268.9075630251</v>
+        <v>-4822268.9075630242</v>
       </c>
       <c r="BB37" s="95">
         <f t="shared" si="33"/>
-        <v>-0.60339778619203788</v>
+        <v>-0.60339778619203777</v>
       </c>
       <c r="BC37" s="78">
         <f>IFERROR(VLOOKUP(C37,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -21439,43 +21439,43 @@
       </c>
       <c r="U38" s="87">
         <f t="shared" si="7"/>
-        <v>133.63636363636363</v>
+        <v>138.09090909090907</v>
       </c>
       <c r="V38" s="88">
         <f t="shared" si="8"/>
-        <v>1.2148760330578512</v>
+        <v>1.2553719008264461</v>
       </c>
       <c r="W38" s="89">
         <f t="shared" si="9"/>
-        <v>23.636363636363626</v>
+        <v>28.090909090909065</v>
       </c>
       <c r="X38" s="89">
         <f t="shared" si="10"/>
-        <v>62.727272727272727</v>
+        <v>64.818181818181813</v>
       </c>
       <c r="Y38" s="89">
         <f t="shared" si="11"/>
-        <v>-47.272727272727273</v>
+        <v>-45.181818181818187</v>
       </c>
       <c r="Z38" s="90">
         <f t="shared" si="12"/>
-        <v>661775454.5454545</v>
+        <v>683834636.36363626</v>
       </c>
       <c r="AA38" s="90">
         <f t="shared" si="13"/>
-        <v>188775454.5454545</v>
+        <v>210834636.36363626</v>
       </c>
       <c r="AB38" s="91">
         <f t="shared" si="14"/>
-        <v>1.399102440899481</v>
+        <v>1.4457391889294635</v>
       </c>
       <c r="AC38" s="92">
         <f t="shared" si="15"/>
-        <v>3.2105263157894739</v>
+        <v>3.05</v>
       </c>
       <c r="AD38" s="93">
         <f t="shared" si="16"/>
-        <v>12123631.578947369</v>
+        <v>11517450</v>
       </c>
       <c r="AE38" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C38),0)</f>
@@ -21515,15 +21515,15 @@
       </c>
       <c r="AN38" s="81">
         <f t="shared" si="22"/>
-        <v>133.63636363636363</v>
+        <v>138.09090909090907</v>
       </c>
       <c r="AO38" s="81">
         <f t="shared" si="23"/>
-        <v>17.636363636363626</v>
+        <v>22.090909090909065</v>
       </c>
       <c r="AP38" s="83">
         <f t="shared" si="24"/>
-        <v>0.15203761755485884</v>
+        <v>0.190438871473354</v>
       </c>
       <c r="AQ38" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C38,"Segment Price","3mio&gt;"),0)</f>
@@ -21711,43 +21711,43 @@
       </c>
       <c r="U39" s="87">
         <f t="shared" si="7"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="V39" s="88">
         <f t="shared" si="8"/>
-        <v>0.54545454545454541</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="W39" s="89">
         <f t="shared" si="9"/>
-        <v>-27.272727272727273</v>
+        <v>-26.181818181818187</v>
       </c>
       <c r="X39" s="89">
         <f t="shared" si="10"/>
-        <v>13.636363636363637</v>
+        <v>14.09090909090909</v>
       </c>
       <c r="Y39" s="89">
         <f t="shared" si="11"/>
-        <v>-46.36363636363636</v>
+        <v>-45.909090909090907</v>
       </c>
       <c r="Z39" s="90">
         <f t="shared" si="12"/>
-        <v>119149090.90909091</v>
+        <v>123120727.27272728</v>
       </c>
       <c r="AA39" s="90">
         <f t="shared" si="13"/>
-        <v>-138850909.09090909</v>
+        <v>-134879272.72727272</v>
       </c>
       <c r="AB39" s="91">
         <f t="shared" si="14"/>
-        <v>0.46181818181818179</v>
+        <v>0.47721212121212125</v>
       </c>
       <c r="AC39" s="92">
         <f t="shared" si="15"/>
-        <v>2.5263157894736841</v>
+        <v>2.4</v>
       </c>
       <c r="AD39" s="93">
         <f t="shared" si="16"/>
-        <v>11279578.947368421</v>
+        <v>10715600</v>
       </c>
       <c r="AE39" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C39),0)</f>
@@ -21787,15 +21787,15 @@
       </c>
       <c r="AN39" s="81">
         <f t="shared" si="22"/>
-        <v>32.727272727272727</v>
+        <v>33.818181818181813</v>
       </c>
       <c r="AO39" s="81">
         <f t="shared" si="23"/>
-        <v>-37.272727272727273</v>
+        <v>-36.181818181818187</v>
       </c>
       <c r="AP39" s="83">
         <f t="shared" si="24"/>
-        <v>-0.53246753246753242</v>
+        <v>-0.51688311688311694</v>
       </c>
       <c r="AQ39" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C39,"Segment Price","3mio&gt;"),0)</f>
@@ -21835,15 +21835,15 @@
       </c>
       <c r="AZ39" s="85">
         <f t="shared" si="31"/>
-        <v>3640666.6666666665</v>
+        <v>3640666.6666666674</v>
       </c>
       <c r="BA39" s="85">
         <f t="shared" si="32"/>
-        <v>94047.619047618937</v>
+        <v>94047.619047619868</v>
       </c>
       <c r="BB39" s="95">
         <f t="shared" si="33"/>
-        <v>2.6517541857436294E-2</v>
+        <v>2.6517541857436554E-2</v>
       </c>
       <c r="BC39" s="78">
         <f>IFERROR(VLOOKUP(C39,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -21983,43 +21983,43 @@
       </c>
       <c r="U40" s="87">
         <f t="shared" si="7"/>
-        <v>125.45454545454545</v>
+        <v>129.63636363636363</v>
       </c>
       <c r="V40" s="88">
         <f t="shared" si="8"/>
-        <v>1.0454545454545454</v>
+        <v>1.0803030303030303</v>
       </c>
       <c r="W40" s="89">
         <f t="shared" si="9"/>
-        <v>5.4545454545454533</v>
+        <v>9.636363636363626</v>
       </c>
       <c r="X40" s="89">
         <f t="shared" si="10"/>
-        <v>40.909090909090907</v>
+        <v>42.272727272727266</v>
       </c>
       <c r="Y40" s="89">
         <f t="shared" si="11"/>
-        <v>-79.090909090909093</v>
+        <v>-77.727272727272734</v>
       </c>
       <c r="Z40" s="90">
         <f t="shared" si="12"/>
-        <v>455601818.18181819</v>
+        <v>470788545.4545455</v>
       </c>
       <c r="AA40" s="90">
         <f t="shared" si="13"/>
-        <v>-60398181.818181813</v>
+        <v>-45211454.545454502</v>
       </c>
       <c r="AB40" s="91">
         <f t="shared" si="14"/>
-        <v>0.88294926004228336</v>
+        <v>0.91238090204369282</v>
       </c>
       <c r="AC40" s="92">
         <f t="shared" si="15"/>
-        <v>3.8947368421052633</v>
+        <v>3.7</v>
       </c>
       <c r="AD40" s="93">
         <f t="shared" si="16"/>
-        <v>18365578.947368421</v>
+        <v>17447300</v>
       </c>
       <c r="AE40" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C40),0)</f>
@@ -22059,15 +22059,15 @@
       </c>
       <c r="AN40" s="81">
         <f t="shared" si="22"/>
-        <v>125.45454545454545</v>
+        <v>129.63636363636363</v>
       </c>
       <c r="AO40" s="81">
         <f t="shared" si="23"/>
-        <v>13.454545454545453</v>
+        <v>17.636363636363626</v>
       </c>
       <c r="AP40" s="83">
         <f t="shared" si="24"/>
-        <v>0.12012987012987011</v>
+        <v>0.15746753246753237</v>
       </c>
       <c r="AQ40" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C40,"Segment Price","3mio&gt;"),0)</f>
@@ -22107,15 +22107,15 @@
       </c>
       <c r="AZ40" s="85">
         <f t="shared" si="31"/>
-        <v>3631608.6956521738</v>
+        <v>3631608.6956521748</v>
       </c>
       <c r="BA40" s="85">
         <f t="shared" si="32"/>
-        <v>47314.578005115036</v>
+        <v>47314.578005115967</v>
       </c>
       <c r="BB40" s="95">
         <f t="shared" si="33"/>
-        <v>1.3200528877405603E-2</v>
+        <v>1.3200528877405863E-2</v>
       </c>
       <c r="BC40" s="78">
         <f>IFERROR(VLOOKUP(C40,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -22255,43 +22255,43 @@
       </c>
       <c r="U41" s="87">
         <f t="shared" si="7"/>
-        <v>130.90909090909091</v>
+        <v>135.27272727272725</v>
       </c>
       <c r="V41" s="88">
         <f t="shared" si="8"/>
-        <v>1.0909090909090908</v>
+        <v>1.1272727272727272</v>
       </c>
       <c r="W41" s="89">
         <f t="shared" si="9"/>
-        <v>10.909090909090907</v>
+        <v>15.272727272727252</v>
       </c>
       <c r="X41" s="89">
         <f t="shared" si="10"/>
-        <v>46.36363636363636</v>
+        <v>47.909090909090907</v>
       </c>
       <c r="Y41" s="89">
         <f t="shared" si="11"/>
-        <v>-73.63636363636364</v>
+        <v>-72.090909090909093</v>
       </c>
       <c r="Z41" s="90">
         <f t="shared" si="12"/>
-        <v>496778181.81818181</v>
+        <v>513337454.5454545</v>
       </c>
       <c r="AA41" s="90">
         <f t="shared" si="13"/>
-        <v>-19221818.181818187</v>
+        <v>-2662545.4545454979</v>
       </c>
       <c r="AB41" s="91">
         <f t="shared" si="14"/>
-        <v>0.9627484143763213</v>
+        <v>0.9948400281888653</v>
       </c>
       <c r="AC41" s="92">
         <f t="shared" si="15"/>
-        <v>3.7894736842105261</v>
+        <v>3.6</v>
       </c>
       <c r="AD41" s="93">
         <f t="shared" si="16"/>
-        <v>17570947.368421052</v>
+        <v>16692400</v>
       </c>
       <c r="AE41" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C41),0)</f>
@@ -22331,15 +22331,15 @@
       </c>
       <c r="AN41" s="81">
         <f t="shared" si="22"/>
-        <v>130.90909090909091</v>
+        <v>135.27272727272725</v>
       </c>
       <c r="AO41" s="81">
         <f t="shared" si="23"/>
-        <v>-11.090909090909093</v>
+        <v>-6.7272727272727479</v>
       </c>
       <c r="AP41" s="83">
         <f t="shared" si="24"/>
-        <v>-7.8104993597951367E-2</v>
+        <v>-4.7375160051216537E-2</v>
       </c>
       <c r="AQ41" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C41,"Segment Price","3mio&gt;"),0)</f>
@@ -22527,43 +22527,43 @@
       </c>
       <c r="U42" s="87">
         <f t="shared" si="7"/>
-        <v>10.90909090909091</v>
+        <v>11.272727272727273</v>
       </c>
       <c r="V42" s="88">
         <f t="shared" si="8"/>
-        <v>0.54545454545454553</v>
+        <v>0.56363636363636371</v>
       </c>
       <c r="W42" s="89">
         <f t="shared" si="9"/>
-        <v>-9.0909090909090899</v>
+        <v>-8.7272727272727266</v>
       </c>
       <c r="X42" s="89">
         <f t="shared" si="10"/>
-        <v>5.454545454545455</v>
+        <v>5.6363636363636367</v>
       </c>
       <c r="Y42" s="89">
         <f t="shared" si="11"/>
-        <v>-14.545454545454545</v>
+        <v>-14.363636363636363</v>
       </c>
       <c r="Z42" s="90">
         <f t="shared" si="12"/>
-        <v>53170909.090909094</v>
+        <v>54943272.727272734</v>
       </c>
       <c r="AA42" s="90">
         <f t="shared" si="13"/>
-        <v>-32829090.909090906</v>
+        <v>-31056727.272727266</v>
       </c>
       <c r="AB42" s="91">
         <f t="shared" si="14"/>
-        <v>0.61826638477801277</v>
+        <v>0.63887526427061314</v>
       </c>
       <c r="AC42" s="92">
         <f t="shared" si="15"/>
-        <v>0.84210526315789469</v>
+        <v>0.8</v>
       </c>
       <c r="AD42" s="93">
         <f t="shared" si="16"/>
-        <v>3500210.5263157897</v>
+        <v>3325200</v>
       </c>
       <c r="AE42" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C42),0)</f>
@@ -22603,15 +22603,15 @@
       </c>
       <c r="AN42" s="81">
         <f t="shared" si="22"/>
-        <v>10.90909090909091</v>
+        <v>11.272727272727273</v>
       </c>
       <c r="AO42" s="81">
         <f t="shared" si="23"/>
-        <v>-3.0909090909090899</v>
+        <v>-2.7272727272727266</v>
       </c>
       <c r="AP42" s="83">
         <f t="shared" si="24"/>
-        <v>-0.22077922077922071</v>
+        <v>-0.19480519480519476</v>
       </c>
       <c r="AQ42" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C42,"Segment Price","3mio&gt;"),0)</f>
@@ -22799,43 +22799,43 @@
       </c>
       <c r="U43" s="87">
         <f t="shared" si="7"/>
-        <v>8.1818181818181817</v>
+        <v>8.4545454545454533</v>
       </c>
       <c r="V43" s="88">
         <f t="shared" si="8"/>
-        <v>0.40909090909090906</v>
+        <v>0.42272727272727267</v>
       </c>
       <c r="W43" s="89">
         <f t="shared" si="9"/>
-        <v>-11.818181818181818</v>
+        <v>-11.545454545454547</v>
       </c>
       <c r="X43" s="89">
         <f t="shared" si="10"/>
-        <v>8.1818181818181817</v>
+        <v>8.4545454545454533</v>
       </c>
       <c r="Y43" s="89">
         <f t="shared" si="11"/>
-        <v>-11.818181818181818</v>
+        <v>-11.545454545454547</v>
       </c>
       <c r="Z43" s="90">
         <f t="shared" si="12"/>
-        <v>36537272.727272727</v>
+        <v>37755181.818181813</v>
       </c>
       <c r="AA43" s="90">
         <f t="shared" si="13"/>
-        <v>-43462727.272727273</v>
+        <v>-42244818.181818187</v>
       </c>
       <c r="AB43" s="91">
         <f t="shared" si="14"/>
-        <v>0.45671590909090909</v>
+        <v>0.47193977272727267</v>
       </c>
       <c r="AC43" s="92">
         <f t="shared" si="15"/>
-        <v>0.89473684210526316</v>
+        <v>0.85</v>
       </c>
       <c r="AD43" s="93">
         <f t="shared" si="16"/>
-        <v>3505421.0526315789</v>
+        <v>3330150</v>
       </c>
       <c r="AE43" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C43),0)</f>
@@ -22875,15 +22875,15 @@
       </c>
       <c r="AN43" s="81">
         <f t="shared" si="22"/>
-        <v>8.1818181818181817</v>
+        <v>8.4545454545454533</v>
       </c>
       <c r="AO43" s="81">
         <f t="shared" si="23"/>
-        <v>0.18181818181818166</v>
+        <v>0.45454545454545325</v>
       </c>
       <c r="AP43" s="83">
         <f t="shared" si="24"/>
-        <v>2.2727272727272707E-2</v>
+        <v>5.6818181818181657E-2</v>
       </c>
       <c r="AQ43" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C43,"Segment Price","3mio&gt;"),0)</f>
@@ -23071,43 +23071,43 @@
       </c>
       <c r="U44" s="87">
         <f t="shared" si="7"/>
-        <v>40.909090909090907</v>
+        <v>42.272727272727266</v>
       </c>
       <c r="V44" s="88">
         <f t="shared" si="8"/>
-        <v>0.68181818181818177</v>
+        <v>0.70454545454545447</v>
       </c>
       <c r="W44" s="89">
         <f t="shared" si="9"/>
-        <v>-19.090909090909093</v>
+        <v>-17.727272727272734</v>
       </c>
       <c r="X44" s="89">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y44" s="89">
         <f t="shared" si="11"/>
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="Z44" s="90">
         <f t="shared" si="12"/>
-        <v>248140909.09090909</v>
+        <v>256412272.72727275</v>
       </c>
       <c r="AA44" s="90">
         <f t="shared" si="13"/>
-        <v>-51859090.909090906</v>
+        <v>-43587727.272727251</v>
       </c>
       <c r="AB44" s="91">
         <f t="shared" si="14"/>
-        <v>0.82713636363636367</v>
+        <v>0.85470757575757583</v>
       </c>
       <c r="AC44" s="92">
         <f t="shared" si="15"/>
-        <v>2.3684210526315788</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" s="93">
         <f t="shared" si="16"/>
-        <v>11000789.47368421</v>
+        <v>10450750</v>
       </c>
       <c r="AE44" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C44),0)</f>
@@ -23147,15 +23147,15 @@
       </c>
       <c r="AN44" s="81">
         <f t="shared" si="22"/>
-        <v>40.909090909090907</v>
+        <v>42.272727272727266</v>
       </c>
       <c r="AO44" s="81">
         <f t="shared" si="23"/>
-        <v>-9.0909090909090935</v>
+        <v>-7.7272727272727337</v>
       </c>
       <c r="AP44" s="83">
         <f t="shared" si="24"/>
-        <v>-0.18181818181818188</v>
+        <v>-0.15454545454545468</v>
       </c>
       <c r="AQ44" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C44,"Segment Price","3mio&gt;"),0)</f>
@@ -23195,15 +23195,15 @@
       </c>
       <c r="AZ44" s="85">
         <f t="shared" si="31"/>
-        <v>6065666.666666667</v>
+        <v>6065666.6666666679</v>
       </c>
       <c r="BA44" s="85">
         <f t="shared" si="32"/>
-        <v>450877.19298245665</v>
+        <v>450877.19298245758</v>
       </c>
       <c r="BB44" s="95">
         <f t="shared" si="33"/>
-        <v>8.0301709457791706E-2</v>
+        <v>8.0301709457791873E-2</v>
       </c>
       <c r="BC44" s="78">
         <f>IFERROR(VLOOKUP(C44,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -23343,43 +23343,43 @@
       </c>
       <c r="U45" s="87">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V45" s="88">
         <f t="shared" si="8"/>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="W45" s="89">
         <f t="shared" si="9"/>
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="X45" s="89">
         <f t="shared" si="10"/>
-        <v>21.81818181818182</v>
+        <v>22.545454545454547</v>
       </c>
       <c r="Y45" s="89">
         <f t="shared" si="11"/>
-        <v>-28.18181818181818</v>
+        <v>-27.454545454545453</v>
       </c>
       <c r="Z45" s="90">
         <f t="shared" si="12"/>
-        <v>136606363.63636363</v>
+        <v>141159909.09090906</v>
       </c>
       <c r="AA45" s="90">
         <f t="shared" si="13"/>
-        <v>-213393636.36363637</v>
+        <v>-208840090.90909094</v>
       </c>
       <c r="AB45" s="91">
         <f t="shared" si="14"/>
-        <v>0.3903038961038961</v>
+        <v>0.40331402597402588</v>
       </c>
       <c r="AC45" s="92">
         <f t="shared" si="15"/>
-        <v>2.0526315789473686</v>
+        <v>1.95</v>
       </c>
       <c r="AD45" s="93">
         <f t="shared" si="16"/>
-        <v>15784789.47368421</v>
+        <v>14995550</v>
       </c>
       <c r="AE45" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C45),0)</f>
@@ -23419,15 +23419,15 @@
       </c>
       <c r="AN45" s="81">
         <f t="shared" si="22"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO45" s="81">
         <f t="shared" si="23"/>
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="AP45" s="83">
         <f t="shared" si="24"/>
-        <v>-0.38775510204081631</v>
+        <v>-0.36734693877551022</v>
       </c>
       <c r="AQ45" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C45,"Segment Price","3mio&gt;"),0)</f>
@@ -23615,43 +23615,43 @@
       </c>
       <c r="U46" s="87">
         <f t="shared" si="7"/>
-        <v>13.636363636363637</v>
+        <v>14.09090909090909</v>
       </c>
       <c r="V46" s="88">
         <f t="shared" si="8"/>
-        <v>0.45454545454545453</v>
+        <v>0.46969696969696967</v>
       </c>
       <c r="W46" s="89">
         <f t="shared" si="9"/>
-        <v>-16.363636363636363</v>
+        <v>-15.90909090909091</v>
       </c>
       <c r="X46" s="89">
         <f t="shared" si="10"/>
-        <v>8.1818181818181817</v>
+        <v>8.4545454545454533</v>
       </c>
       <c r="Y46" s="89">
         <f t="shared" si="11"/>
-        <v>-21.81818181818182</v>
+        <v>-21.545454545454547</v>
       </c>
       <c r="Z46" s="90">
         <f t="shared" si="12"/>
-        <v>122986363.63636364</v>
+        <v>127085909.09090909</v>
       </c>
       <c r="AA46" s="90">
         <f t="shared" si="13"/>
-        <v>-87013636.36363636</v>
+        <v>-82914090.909090906</v>
       </c>
       <c r="AB46" s="91">
         <f t="shared" si="14"/>
-        <v>0.58564935064935064</v>
+        <v>0.60517099567099564</v>
       </c>
       <c r="AC46" s="92">
         <f t="shared" si="15"/>
-        <v>1.3157894736842106</v>
+        <v>1.25</v>
       </c>
       <c r="AD46" s="93">
         <f t="shared" si="16"/>
-        <v>8679210.5263157897</v>
+        <v>8245250</v>
       </c>
       <c r="AE46" s="78">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C46),0)</f>
@@ -23691,15 +23691,15 @@
       </c>
       <c r="AN46" s="81">
         <f t="shared" si="22"/>
-        <v>13.636363636363637</v>
+        <v>14.09090909090909</v>
       </c>
       <c r="AO46" s="81">
         <f t="shared" si="23"/>
-        <v>-15.363636363636363</v>
+        <v>-14.90909090909091</v>
       </c>
       <c r="AP46" s="83">
         <f t="shared" si="24"/>
-        <v>-0.52978056426332287</v>
+        <v>-0.51410658307210033</v>
       </c>
       <c r="AQ46" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C46,"Segment Price","3mio&gt;"),0)</f>
@@ -23887,43 +23887,43 @@
       </c>
       <c r="U47" s="119">
         <f t="shared" si="7"/>
-        <v>54.545454545454547</v>
+        <v>56.36363636363636</v>
       </c>
       <c r="V47" s="120">
         <f t="shared" si="8"/>
-        <v>0.90909090909090906</v>
+        <v>0.93939393939393934</v>
       </c>
       <c r="W47" s="121">
         <f t="shared" si="9"/>
-        <v>-5.4545454545454533</v>
+        <v>-3.6363636363636402</v>
       </c>
       <c r="X47" s="121">
         <f t="shared" si="10"/>
-        <v>43.63636363636364</v>
+        <v>45.090909090909093</v>
       </c>
       <c r="Y47" s="121">
         <f t="shared" si="11"/>
-        <v>-16.36363636363636</v>
+        <v>-14.909090909090907</v>
       </c>
       <c r="Z47" s="122">
         <f t="shared" si="12"/>
-        <v>350945454.54545456</v>
+        <v>362643636.36363637</v>
       </c>
       <c r="AA47" s="122">
         <f t="shared" si="13"/>
-        <v>-69054545.454545438</v>
+        <v>-57356363.636363626</v>
       </c>
       <c r="AB47" s="123">
         <f t="shared" si="14"/>
-        <v>0.83558441558441565</v>
+        <v>0.86343722943722945</v>
       </c>
       <c r="AC47" s="124">
         <f t="shared" si="15"/>
-        <v>2.1052631578947367</v>
+        <v>2</v>
       </c>
       <c r="AD47" s="125">
         <f t="shared" si="16"/>
-        <v>15332631.578947369</v>
+        <v>14566000</v>
       </c>
       <c r="AE47" s="110">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH IQOO'!$A$6,"ID Store",$C47),0)</f>
@@ -23963,15 +23963,15 @@
       </c>
       <c r="AN47" s="113">
         <f t="shared" si="22"/>
-        <v>54.545454545454547</v>
+        <v>56.36363636363636</v>
       </c>
       <c r="AO47" s="113">
         <f t="shared" si="23"/>
-        <v>-3.4545454545454533</v>
+        <v>-1.6363636363636402</v>
       </c>
       <c r="AP47" s="115">
         <f t="shared" si="24"/>
-        <v>-5.9561128526645746E-2</v>
+        <v>-2.8213166144200694E-2</v>
       </c>
       <c r="AQ47" s="114">
         <f>IFERROR(GETPIVOTDATA("Sum of Qty",'[1]DATA LAST MONTH DEVICE'!$A$6,"ID Store",$C47,"Segment Price","3mio&gt;"),0)</f>
@@ -24011,15 +24011,15 @@
       </c>
       <c r="AZ47" s="117">
         <f t="shared" si="31"/>
-        <v>6434000</v>
+        <v>6434000.0000000009</v>
       </c>
       <c r="BA47" s="117">
         <f t="shared" si="32"/>
-        <v>-530217.39130434766</v>
+        <v>-530217.39130434673</v>
       </c>
       <c r="BB47" s="127">
         <f t="shared" si="33"/>
-        <v>-7.6134526180412901E-2</v>
+        <v>-7.6134526180412762E-2</v>
       </c>
       <c r="BC47" s="110">
         <f>IFERROR(VLOOKUP(C47,'[1]TARGET THIS MONTH'!C:U,15,0),0)</f>
@@ -24152,43 +24152,43 @@
       </c>
       <c r="U48" s="11">
         <f>SUM(U5:U47)</f>
-        <v>3504.545454545455</v>
+        <v>3621.3636363636369</v>
       </c>
       <c r="V48" s="6">
         <f>U48/G48</f>
-        <v>1.0307486631016043</v>
+        <v>1.0651069518716578</v>
       </c>
       <c r="W48" s="7">
         <f t="shared" si="9"/>
-        <v>104.54545454545496</v>
+        <v>221.36363636363694</v>
       </c>
       <c r="X48" s="7">
         <f>SUM(X5:X47)</f>
-        <v>1333.636363636364</v>
+        <v>1378.0909090909092</v>
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="11"/>
-        <v>-2066.363636363636</v>
+        <v>-2021.9090909090908</v>
       </c>
       <c r="Z48" s="9">
         <f>SUM(Z5:Z47)</f>
-        <v>13495677272.727274</v>
+        <v>13945533181.818182</v>
       </c>
       <c r="AA48" s="9">
         <f t="shared" si="13"/>
-        <v>-2163322727.2727261</v>
+        <v>-1713466818.181818</v>
       </c>
       <c r="AB48" s="12">
         <f>Z48/H48</f>
-        <v>0.86184796428426302</v>
+        <v>0.89057622976040496</v>
       </c>
       <c r="AC48" s="13">
         <f>SUM(AC5:AC47)</f>
-        <v>111.31578947368422</v>
+        <v>105.75</v>
       </c>
       <c r="AD48" s="5">
         <f>SUM(AD5:AD47)</f>
-        <v>563715000.00000024</v>
+        <v>535529250</v>
       </c>
       <c r="AE48" s="4">
         <f>SUM(AE5:AE47)</f>
@@ -24228,15 +24228,15 @@
       </c>
       <c r="AN48" s="7">
         <f>SUM(AN5:AN47)</f>
-        <v>3504.545454545455</v>
+        <v>3621.3636363636369</v>
       </c>
       <c r="AO48" s="7">
         <f t="shared" si="23"/>
-        <v>62.545454545454959</v>
+        <v>179.36363636363694</v>
       </c>
       <c r="AP48" s="8">
         <f>AO48/AM48</f>
-        <v>1.8171253499551121E-2</v>
+        <v>5.2110295282869534E-2</v>
       </c>
       <c r="AQ48" s="2">
         <f>SUM(AQ5:AQ47)</f>
@@ -24276,15 +24276,15 @@
       </c>
       <c r="AZ48" s="9">
         <f>Z48/U48</f>
-        <v>3850906.6147859921</v>
+        <v>3850906.6147859916</v>
       </c>
       <c r="BA48" s="9">
         <f t="shared" si="32"/>
-        <v>-749646.94204148138</v>
+        <v>-749646.94204148185</v>
       </c>
       <c r="BB48" s="12">
         <f>BA48/AY48</f>
-        <v>-0.16294711772868381</v>
+        <v>-0.16294711772868392</v>
       </c>
       <c r="BC48" s="4">
         <f>SUM(BC5:BC47)</f>
